--- a/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
+++ b/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf · Fecha de publicación: 05 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026</t>
+          <t>5 de agosto de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
+++ b/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
@@ -16978,7 +16978,7 @@
         <v>45566</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>113.1</v>
+        <v>109.31</v>
       </c>
       <c r="D387" s="7" t="n">
         <v>103.67</v>
@@ -17021,7 +17021,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>113.7</v>
+        <v>109.8</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>103.33</v>
@@ -17064,7 +17064,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>109.7</v>
+        <v>106.09</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>101.15</v>
@@ -17107,7 +17107,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>107.4</v>
+        <v>105.2</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>100.26</v>
@@ -17150,7 +17150,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>107.3</v>
+        <v>105.94</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>102.49</v>
@@ -17193,7 +17193,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>107.9</v>
+        <v>106.09</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>104.74</v>
@@ -17236,7 +17236,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>105.6</v>
+        <v>102.19</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>99.77</v>
@@ -17279,7 +17279,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>106.8</v>
+        <v>104.55</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>103.92</v>
@@ -17322,7 +17322,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>105.6</v>
+        <v>102.97</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>102.09</v>
@@ -17365,7 +17365,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>107.5</v>
+        <v>104.84</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>101.17</v>
@@ -17408,7 +17408,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>103.9</v>
+        <v>101.93</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>100.13</v>
@@ -17451,7 +17451,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>101</v>
+        <v>102.03</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>98.14</v>
@@ -17494,7 +17494,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>102.2</v>
+        <v>103.03</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>102.34</v>
@@ -17537,7 +17537,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>102.8</v>
+        <v>103.61</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>103.93</v>
@@ -17580,7 +17580,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>103.6</v>
+        <v>104.06</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>104.88</v>
@@ -17623,7 +17623,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>102.3</v>
+        <v>103.02</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>103.85</v>
@@ -17666,7 +17666,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>101.1</v>
+        <v>102.66</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>104.19</v>
@@ -17709,7 +17709,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>102</v>
+        <v>103.26</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>101.99</v>
@@ -17752,7 +17752,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>107.4</v>
+        <v>107.52</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>108.64</v>
@@ -17795,7 +17795,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>107.1</v>
+        <v>107.08</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>106.03</v>
@@ -37520,10 +37520,10 @@
         <v>45566</v>
       </c>
       <c r="C387" s="9" t="n">
-        <v>0.001</v>
+        <v>-0.015048</v>
       </c>
       <c r="D387" s="9" t="n">
-        <v>-0.045</v>
+        <v>-0.033766</v>
       </c>
       <c r="E387" s="9" t="n">
         <v>-0.046713</v>
@@ -37538,10 +37538,10 @@
         <v>0.023313</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>-0.035</v>
+        <v>-0.060451</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.092805</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>0.000648</v>
@@ -37572,10 +37572,10 @@
         <v>45597</v>
       </c>
       <c r="C388" s="10" t="n">
-        <v>0.001</v>
+        <v>0.004483</v>
       </c>
       <c r="D388" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.00372</v>
       </c>
       <c r="E388" s="10" t="n">
         <v>-0.00328</v>
@@ -37590,10 +37590,10 @@
         <v>0.047789</v>
       </c>
       <c r="I388" s="10" t="n">
-        <v>0.068</v>
+        <v>0.04592</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>-0.148</v>
+        <v>-0.113549</v>
       </c>
       <c r="K388" s="10" t="n">
         <v>0.057778</v>
@@ -37624,10 +37624,10 @@
         <v>45627</v>
       </c>
       <c r="C389" s="9" t="n">
-        <v>-0.026</v>
+        <v>-0.033789</v>
       </c>
       <c r="D389" s="9" t="n">
-        <v>-0.041</v>
+        <v>-0.050054</v>
       </c>
       <c r="E389" s="9" t="n">
         <v>-0.021097</v>
@@ -37642,10 +37642,10 @@
         <v>-0.006909</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>0.043</v>
+        <v>0.013716</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>-0.171</v>
+        <v>-0.150542</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>-0.018771</v>
@@ -37676,46 +37676,46 @@
         <v>45658</v>
       </c>
       <c r="C390" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.008389000000000001</v>
       </c>
       <c r="D390" s="10" t="n">
-        <v>-0.059</v>
+        <v>-0.064972</v>
       </c>
       <c r="E390" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.008799</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>-0.09</v>
+        <v>-0.08896</v>
       </c>
       <c r="G390" s="10" t="n">
-        <v>-0.018</v>
+        <v>-0.010079</v>
       </c>
       <c r="H390" s="10" t="n">
-        <v>-0.023</v>
+        <v>-0.034873</v>
       </c>
       <c r="I390" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.018749</v>
       </c>
       <c r="J390" s="10" t="n">
-        <v>-0.142</v>
+        <v>-0.150955</v>
       </c>
       <c r="K390" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.06445099999999999</v>
       </c>
       <c r="L390" s="10" t="n">
-        <v>0.022</v>
+        <v>-0.021894</v>
       </c>
       <c r="M390" s="10" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.112933</v>
       </c>
       <c r="N390" s="10" t="n">
-        <v>-0.016</v>
+        <v>-0.016505</v>
       </c>
       <c r="O390" s="10" t="n">
-        <v>-0.136</v>
+        <v>-0.133866</v>
       </c>
       <c r="P390" s="10" t="n">
-        <v>-0.001</v>
+        <v>-0.002183</v>
       </c>
     </row>
     <row r="391">
@@ -37728,46 +37728,46 @@
         <v>45689</v>
       </c>
       <c r="C391" s="9" t="n">
-        <v>0.001</v>
+        <v>0.007034</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.06</v>
+        <v>-0.057222</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>0.017</v>
+        <v>0.022242</v>
       </c>
       <c r="F391" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.040805</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.007209</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.063</v>
+        <v>-0.06690400000000001</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>0.128</v>
+        <v>0.134879</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>-0.168</v>
+        <v>-0.158449</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>-0.021</v>
+        <v>-0.048798</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>0.021</v>
+        <v>-0.014432</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.077</v>
+        <v>-0.083744</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.093</v>
+        <v>-0.080612</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>-0.081</v>
+        <v>-0.07786</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.080017</v>
       </c>
     </row>
     <row r="392">
@@ -37780,46 +37780,46 @@
         <v>45717</v>
       </c>
       <c r="C392" s="10" t="n">
-        <v>0.003</v>
+        <v>0.001416</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.047</v>
+        <v>-0.050139</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>0.008</v>
+        <v>0.021953</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.023403</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.024142</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.075</v>
+        <v>-0.08501400000000001</v>
       </c>
       <c r="I392" s="10" t="n">
-        <v>0.147</v>
+        <v>0.165855</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>-0.171</v>
+        <v>-0.168667</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>-0.066</v>
+        <v>-0.090119</v>
       </c>
       <c r="L392" s="10" t="n">
-        <v>-0.1</v>
+        <v>-0.12328</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.045168</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.08</v>
+        <v>-0.082334</v>
       </c>
       <c r="O392" s="10" t="n">
-        <v>-0.148</v>
+        <v>-0.146324</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.077</v>
+        <v>-0.07979700000000001</v>
       </c>
     </row>
     <row r="393">
@@ -37832,46 +37832,46 @@
         <v>45748</v>
       </c>
       <c r="C393" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.036761</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.077</v>
+        <v>-0.088891</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.047451</v>
       </c>
       <c r="F393" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.073286</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.022</v>
+        <v>-0.020089</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.091</v>
+        <v>-0.096165</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>0.024</v>
+        <v>-0.005822</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.118</v>
+        <v>-0.130797</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>-0.083</v>
+        <v>-0.08361</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>-0.143</v>
+        <v>-0.152479</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.012811</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.091</v>
+        <v>-0.097068</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>-0.073</v>
+        <v>-0.08448</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.088647</v>
       </c>
     </row>
     <row r="394">
@@ -37884,46 +37884,46 @@
         <v>45778</v>
       </c>
       <c r="C394" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023094</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.067</v>
+        <v>-0.06443</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>0.014</v>
+        <v>0.041596</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.050872</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.082</v>
+        <v>-0.077199</v>
       </c>
       <c r="I394" s="10" t="n">
-        <v>0.079</v>
+        <v>0.086093</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>-0.171</v>
+        <v>-0.185542</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>-0.034</v>
+        <v>-0.027668</v>
       </c>
       <c r="L394" s="10" t="n">
-        <v>-0.055</v>
+        <v>-0.06701699999999999</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.019</v>
+        <v>0.027527</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.106</v>
+        <v>-0.104474</v>
       </c>
       <c r="O394" s="10" t="n">
-        <v>-0.267</v>
+        <v>-0.258816</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.073035</v>
       </c>
     </row>
     <row r="395">
@@ -37936,46 +37936,46 @@
         <v>45809</v>
       </c>
       <c r="C395" s="9" t="n">
-        <v>-0.014</v>
+        <v>-0.015112</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.072426</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.01761</v>
       </c>
       <c r="F395" s="9" t="n">
-        <v>-0.033</v>
+        <v>-0.047579</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.013453</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.114</v>
+        <v>-0.109162</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>0.118</v>
+        <v>0.127166</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>-0.138</v>
+        <v>-0.168133</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>-0.132</v>
+        <v>-0.121275</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>-0.155</v>
+        <v>-0.162111</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.114</v>
+        <v>-0.08884499999999999</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.096</v>
+        <v>-0.096884</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>-0.148</v>
+        <v>-0.141362</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.081</v>
+        <v>-0.083341</v>
       </c>
     </row>
     <row r="396">
@@ -37988,46 +37988,46 @@
         <v>45839</v>
       </c>
       <c r="C396" s="10" t="n">
-        <v>0.016</v>
+        <v>0.018161</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.076462</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.013</v>
+        <v>-0.009011999999999999</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>-0.075</v>
+        <v>-0.085428</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>0.049</v>
+        <v>0.041295</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.059</v>
+        <v>-0.060399</v>
       </c>
       <c r="I396" s="10" t="n">
-        <v>0.046</v>
+        <v>0.048605</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>-0.176</v>
+        <v>-0.193244</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>-0.114</v>
+        <v>-0.113206</v>
       </c>
       <c r="L396" s="10" t="n">
-        <v>-0.172</v>
+        <v>-0.179896</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.049</v>
+        <v>-0.044993</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.030429</v>
       </c>
       <c r="O396" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.049179</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.023</v>
+        <v>-0.02938</v>
       </c>
     </row>
     <row r="397">
@@ -38040,46 +38040,46 @@
         <v>45870</v>
       </c>
       <c r="C397" s="9" t="n">
-        <v>-0.027</v>
+        <v>-0.027757</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.089</v>
+        <v>-0.09371400000000001</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.015</v>
+        <v>-0.01028</v>
       </c>
       <c r="F397" s="9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06977</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.031</v>
+        <v>-0.038642</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.105</v>
+        <v>-0.11661</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>0.1</v>
+        <v>0.114345</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>-0.185</v>
+        <v>-0.193146</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.125056</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>-0.123</v>
+        <v>-0.136875</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.056</v>
+        <v>-0.12077</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.119</v>
+        <v>-0.11674</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>-0.154</v>
+        <v>-0.153669</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.11</v>
+        <v>-0.105321</v>
       </c>
     </row>
     <row r="398">
@@ -38092,46 +38092,46 @@
         <v>45901</v>
       </c>
       <c r="C398" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.0009810000000000001</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.08064499999999999</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.026</v>
+        <v>-0.019874</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>-0.102</v>
+        <v>-0.097563</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>0.019</v>
+        <v>0.01698</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.061</v>
+        <v>-0.06492000000000001</v>
       </c>
       <c r="I398" s="10" t="n">
-        <v>-0.02</v>
+        <v>-0.013778</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.164</v>
+        <v>-0.163115</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>-0.106</v>
+        <v>-0.110615</v>
       </c>
       <c r="L398" s="10" t="n">
-        <v>-0.168</v>
+        <v>-0.171639</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.045442</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.033</v>
+        <v>-0.033193</v>
       </c>
       <c r="O398" s="10" t="n">
-        <v>-0.164</v>
+        <v>-0.158983</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.006</v>
+        <v>-0.006402</v>
       </c>
     </row>
     <row r="399">
@@ -38144,46 +38144,46 @@
         <v>45931</v>
       </c>
       <c r="C399" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009801000000000001</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.058</v>
+        <v>-0.057451</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>0.039</v>
+        <v>0.042796</v>
       </c>
       <c r="F399" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.012829</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.022</v>
+        <v>-0.023394</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.103</v>
+        <v>-0.106576</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>0.118</v>
+        <v>0.123451</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>-0.126</v>
+        <v>-0.120576</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>-0.118</v>
+        <v>-0.121106</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>-0.171</v>
+        <v>-0.17199</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.047</v>
+        <v>-0.052782</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.094</v>
+        <v>-0.095293</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>-0.132</v>
+        <v>-0.128501</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.089837</v>
       </c>
     </row>
     <row r="400">
@@ -38196,46 +38196,46 @@
         <v>45962</v>
       </c>
       <c r="C400" s="10" t="n">
-        <v>0.004</v>
+        <v>0.005629</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.057</v>
+        <v>-0.056375</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>0.015</v>
+        <v>0.015536</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>0.006</v>
+        <v>0.005807</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.000386</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.116</v>
+        <v>-0.117732</v>
       </c>
       <c r="I400" s="10" t="n">
-        <v>0.092</v>
+        <v>0.09221</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06801500000000001</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>-0.152</v>
+        <v>-0.153805</v>
       </c>
       <c r="L400" s="10" t="n">
-        <v>-0.187</v>
+        <v>-0.191459</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.101</v>
+        <v>-0.103646</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.091</v>
+        <v>-0.090767</v>
       </c>
       <c r="O400" s="10" t="n">
-        <v>-0.191</v>
+        <v>-0.186943</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.075</v>
+        <v>-0.077817</v>
       </c>
     </row>
     <row r="401">
@@ -38248,46 +38248,46 @@
         <v>45992</v>
       </c>
       <c r="C401" s="9" t="n">
-        <v>0.005</v>
+        <v>0.004343</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.019135</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009141</v>
       </c>
       <c r="F401" s="9" t="n">
-        <v>0.041</v>
+        <v>0.036876</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>-0.003</v>
+        <v>-0.001546</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.079</v>
+        <v>-0.078316</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>0.142</v>
+        <v>0.139663</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>-0.03</v>
+        <v>-0.032787</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>-0.118</v>
+        <v>-0.118588</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.165981</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.053</v>
+        <v>-0.054836</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.048774</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>-0.027</v>
+        <v>-0.034135</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.05</v>
+        <v>-0.049122</v>
       </c>
     </row>
     <row r="402">
@@ -38300,46 +38300,46 @@
         <v>46023</v>
       </c>
       <c r="C402" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.009993999999999999</v>
       </c>
       <c r="D402" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.020722</v>
       </c>
       <c r="E402" s="10" t="n">
-        <v>-0.008</v>
+        <v>-0.009821</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>0.038</v>
+        <v>0.035807</v>
       </c>
       <c r="G402" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.006871</v>
       </c>
       <c r="H402" s="10" t="n">
-        <v>-0.08</v>
+        <v>-0.07532899999999999</v>
       </c>
       <c r="I402" s="10" t="n">
-        <v>0.079</v>
+        <v>0.077316</v>
       </c>
       <c r="J402" s="10" t="n">
-        <v>0</v>
+        <v>-0.000807</v>
       </c>
       <c r="K402" s="10" t="n">
-        <v>-0.111</v>
+        <v>-0.107851</v>
       </c>
       <c r="L402" s="10" t="n">
-        <v>-0.133</v>
+        <v>-0.141022</v>
       </c>
       <c r="M402" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.07845100000000001</v>
       </c>
       <c r="N402" s="10" t="n">
-        <v>-0.052</v>
+        <v>-0.048812</v>
       </c>
       <c r="O402" s="10" t="n">
-        <v>-0.036</v>
+        <v>-0.038568</v>
       </c>
       <c r="P402" s="10" t="n">
-        <v>-0.063</v>
+        <v>-0.058026</v>
       </c>
     </row>
     <row r="403">
@@ -38352,46 +38352,46 @@
         <v>46054</v>
       </c>
       <c r="C403" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.003494</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.036</v>
+        <v>-0.030961</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>0.001</v>
+        <v>0.003274</v>
       </c>
       <c r="F403" s="9" t="n">
-        <v>0.015</v>
+        <v>0.016587</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>-0.023</v>
+        <v>-0.015299</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>-0.091</v>
+        <v>-0.08286399999999999</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>0.018</v>
+        <v>0.017306</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.01</v>
+        <v>0.014874</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>-0.136</v>
+        <v>-0.12758</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>-0.193</v>
+        <v>-0.193103</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>-0.075</v>
+        <v>-0.059824</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.057</v>
+        <v>-0.05111</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>-0.149</v>
+        <v>-0.148554</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.047</v>
+        <v>-0.037107</v>
       </c>
     </row>
     <row r="404">
@@ -38404,46 +38404,46 @@
         <v>46082</v>
       </c>
       <c r="C404" s="10" t="n">
-        <v>0.004</v>
+        <v>0.005845</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.026675</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.021115</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.026255</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>0.031</v>
+        <v>0.03236</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.029762</v>
       </c>
       <c r="I404" s="10" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.08277</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>0.024</v>
+        <v>0.03482</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.073</v>
+        <v>-0.073404</v>
       </c>
       <c r="L404" s="10" t="n">
-        <v>-0.131</v>
+        <v>-0.129176</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.017345</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>-0.016</v>
+        <v>-0.01184</v>
       </c>
       <c r="O404" s="10" t="n">
-        <v>0.064</v>
+        <v>0.06449199999999999</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.016874</v>
       </c>
     </row>
     <row r="405">
@@ -38456,46 +38456,46 @@
         <v>46113</v>
       </c>
       <c r="C405" s="9" t="n">
-        <v>0.04</v>
+        <v>0.041255</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.051</v>
+        <v>0.052158</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>0.065</v>
+        <v>0.065202</v>
       </c>
       <c r="F405" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.088904</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.02</v>
+        <v>0.021377</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011295</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>0.167</v>
+        <v>0.163739</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.011</v>
+        <v>0.022021</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>-0.106</v>
+        <v>-0.102228</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.078404</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>-0.124</v>
+        <v>-0.122099</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08785800000000001</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.01331</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.098</v>
+        <v>0.100659</v>
       </c>
     </row>
     <row r="406">
@@ -38508,46 +38508,46 @@
         <v>46143</v>
       </c>
       <c r="C406" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.004092</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.024</v>
+        <v>0.024199</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.024024</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>0.02</v>
+        <v>0.020304</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.015</v>
+        <v>0.015392</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.025</v>
+        <v>0.025012</v>
       </c>
       <c r="I406" s="10" t="n">
-        <v>-0.054</v>
+        <v>-0.054435</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>0.118</v>
+        <v>0.117552</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>-0.077</v>
+        <v>-0.077236</v>
       </c>
       <c r="L406" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.049835</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>-0.091</v>
+        <v>-0.09073100000000001</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.089</v>
+        <v>0.08930399999999999</v>
       </c>
       <c r="O406" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.071329</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>0.097</v>
+        <v>0.09743300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -59442,19 +59442,19 @@
         <v>91.53</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.029</v>
+        <v>-0.045966</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>0.047</v>
+        <v>0.03116</v>
       </c>
       <c r="L387" s="7" t="n">
         <v>125.59</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>-0.166</v>
+        <v>-0.095564</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>0.034</v>
+        <v>0.089361</v>
       </c>
       <c r="O387" s="7" t="n">
         <v>121.97</v>
@@ -59497,19 +59497,19 @@
         <v>97.25</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.059599</v>
       </c>
       <c r="K388" s="10" t="n">
-        <v>0.049</v>
+        <v>0.033895</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>124.25</v>
       </c>
       <c r="M388" s="10" t="n">
-        <v>-0.147</v>
+        <v>-0.111421</v>
       </c>
       <c r="N388" s="10" t="n">
-        <v>0.014</v>
+        <v>0.067721</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>121.22</v>
@@ -59552,19 +59552,19 @@
         <v>83.88</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>0.032</v>
+        <v>0.001074</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>0.048</v>
+        <v>0.031246</v>
       </c>
       <c r="L389" s="7" t="n">
         <v>134.91</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>-0.164</v>
+        <v>-0.135026</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>-0.004</v>
+        <v>0.045963</v>
       </c>
       <c r="O389" s="7" t="n">
         <v>116.23</v>
@@ -59644,46 +59644,46 @@
         <v>98.64</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.078</v>
+        <v>-0.080022</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>-0.074</v>
+        <v>-0.077477</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.052</v>
+        <v>-0.046755</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.079</v>
+        <v>-0.07618</v>
       </c>
       <c r="I391" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>0.141</v>
+        <v>0.140825</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>0.056</v>
+        <v>0.050031</v>
       </c>
       <c r="L391" s="7" t="n">
         <v>103.42</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.18</v>
+        <v>-0.17211</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.174</v>
+        <v>-0.166833</v>
       </c>
       <c r="O391" s="7" t="n">
         <v>103.31</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.104</v>
+        <v>-0.113067</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.078884</v>
       </c>
     </row>
     <row r="392">
@@ -59699,46 +59699,46 @@
         <v>105.87</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.005915</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>-0.049</v>
+        <v>-0.053793</v>
       </c>
       <c r="F392" s="6" t="n">
         <v>103.35</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.001</v>
+        <v>0.001356</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.050219</v>
       </c>
       <c r="I392" s="6" t="n">
         <v>105.05</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>0.205</v>
+        <v>0.204564</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>0.108</v>
+        <v>0.103742</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>101.47</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.159</v>
+        <v>-0.160156</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.164</v>
+        <v>-0.164661</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>108.8</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.013689</v>
       </c>
       <c r="Q392" s="10" t="n">
-        <v>-0.047</v>
+        <v>-0.057574</v>
       </c>
     </row>
     <row r="393">
@@ -59754,46 +59754,46 @@
         <v>100.25</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.125</v>
+        <v>-0.131809</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.074395</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>98.39</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.100886</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.061</v>
+        <v>-0.06349399999999999</v>
       </c>
       <c r="I393" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.037</v>
+        <v>-0.048008</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>0.067</v>
+        <v>0.061543</v>
       </c>
       <c r="L393" s="7" t="n">
         <v>105.43</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.139</v>
+        <v>-0.146316</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.158</v>
+        <v>-0.160082</v>
       </c>
       <c r="O393" s="7" t="n">
         <v>102.39</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.16</v>
+        <v>-0.16389</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>-0.077</v>
+        <v>-0.085881</v>
       </c>
     </row>
     <row r="394">
@@ -59809,46 +59809,46 @@
         <v>107.78</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.06594999999999999</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.072632</v>
       </c>
       <c r="F394" s="6" t="n">
         <v>108.65</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>-0.043</v>
+        <v>-0.041634</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.058</v>
+        <v>-0.058827</v>
       </c>
       <c r="I394" s="6" t="n">
         <v>117.83</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>0.096</v>
+        <v>0.102451</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>0.074</v>
+        <v>0.07116500000000001</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.175</v>
+        <v>-0.182241</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.162</v>
+        <v>-0.164421</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>106.76</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.103</v>
+        <v>-0.093179</v>
       </c>
       <c r="Q394" s="10" t="n">
-        <v>-0.082</v>
+        <v>-0.087368</v>
       </c>
     </row>
     <row r="395">
@@ -59864,46 +59864,46 @@
         <v>98.92</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.064</v>
+        <v>-0.068023</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.07188899999999999</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.032</v>
+        <v>-0.04444</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.054</v>
+        <v>-0.05654</v>
       </c>
       <c r="I395" s="7" t="n">
         <v>87.73999999999999</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>0.12</v>
+        <v>0.127039</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>0.082</v>
+        <v>0.079336</v>
       </c>
       <c r="L395" s="7" t="n">
         <v>104.88</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.137</v>
+        <v>-0.161966</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.159</v>
+        <v>-0.164006</v>
       </c>
       <c r="O395" s="7" t="n">
         <v>102.41</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.097</v>
+        <v>-0.092432</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.088196</v>
       </c>
     </row>
     <row r="396">
@@ -59919,46 +59919,46 @@
         <v>106.74</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.066</v>
+        <v>-0.068993</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.068</v>
+        <v>-0.07146</v>
       </c>
       <c r="F396" s="6" t="n">
         <v>102.77</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.078957</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.057</v>
+        <v>-0.059907</v>
       </c>
       <c r="I396" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>0.055</v>
+        <v>0.058786</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>0.078</v>
+        <v>0.076241</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>105.87</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.172</v>
+        <v>-0.188611</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.161</v>
+        <v>-0.167692</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>111.33</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.059</v>
+        <v>-0.058122</v>
       </c>
       <c r="Q396" s="10" t="n">
-        <v>-0.081</v>
+        <v>-0.0838</v>
       </c>
     </row>
     <row r="397">
@@ -59974,46 +59974,46 @@
         <v>102.22</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.104</v>
+        <v>-0.110434</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.073</v>
+        <v>-0.076501</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>101.61</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.074</v>
+        <v>-0.07391499999999999</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.061709</v>
       </c>
       <c r="I397" s="7" t="n">
         <v>91.92</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09912700000000001</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>0.079</v>
+        <v>0.07893500000000001</v>
       </c>
       <c r="L397" s="7" t="n">
         <v>112.27</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.179</v>
+        <v>-0.189094</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.164</v>
+        <v>-0.170628</v>
       </c>
       <c r="O397" s="7" t="n">
         <v>102.94</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.137</v>
+        <v>-0.148693</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.092241</v>
       </c>
     </row>
     <row r="398">
@@ -60029,46 +60029,46 @@
         <v>99.59</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.067</v>
+        <v>-0.067247</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.076</v>
+        <v>-0.07550800000000001</v>
       </c>
       <c r="F398" s="6" t="n">
         <v>94.42</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>-0.106</v>
+        <v>-0.10832</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.067</v>
+        <v>-0.066858</v>
       </c>
       <c r="I398" s="6" t="n">
         <v>85.19</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.028288</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>0.067</v>
+        <v>0.06715500000000001</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>104.59</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.163</v>
+        <v>-0.169591</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.171</v>
+        <v>-0.170513</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>105.57</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.020596</v>
       </c>
       <c r="Q398" s="10" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.084797</v>
       </c>
     </row>
     <row r="399">
@@ -60084,46 +60084,46 @@
         <v>107.9</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.056241</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>-0.074</v>
+        <v>-0.07352300000000001</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.007</v>
+        <v>-0.008817999999999999</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.061</v>
+        <v>-0.060994</v>
       </c>
       <c r="I399" s="7" t="n">
         <v>103.82</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>0.135</v>
+        <v>0.134273</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>0.074</v>
+        <v>0.074062</v>
       </c>
       <c r="L399" s="7" t="n">
         <v>110.07</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.122</v>
+        <v>-0.123577</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.167</v>
+        <v>-0.165838</v>
       </c>
       <c r="O399" s="7" t="n">
         <v>109.17</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.105</v>
+        <v>-0.104944</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.08691599999999999</v>
       </c>
     </row>
     <row r="400">
@@ -60139,46 +60139,46 @@
         <v>107.74</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.064</v>
+        <v>-0.065163</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>-0.073</v>
+        <v>-0.072736</v>
       </c>
       <c r="F400" s="6" t="n">
         <v>111.27</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>0.013</v>
+        <v>0.010627</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.054</v>
+        <v>-0.054291</v>
       </c>
       <c r="I400" s="6" t="n">
         <v>107.18</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>0.103</v>
+        <v>0.102108</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>0.077</v>
+        <v>0.07682600000000001</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>115.79</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.065</v>
+        <v>-0.068089</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.158</v>
+        <v>-0.15707</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>103.66</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.145</v>
+        <v>-0.144861</v>
       </c>
       <c r="Q400" s="10" t="n">
-        <v>-0.093</v>
+        <v>-0.092401</v>
       </c>
     </row>
     <row r="401">
@@ -60194,46 +60194,46 @@
         <v>111.63</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>0</v>
+        <v>-0.002413</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>-0.067</v>
+        <v>-0.06684900000000001</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>112.38</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>0.043</v>
+        <v>0.03892</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.046</v>
+        <v>-0.046442</v>
       </c>
       <c r="I401" s="7" t="n">
         <v>94.72</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>0.133</v>
+        <v>0.129232</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>0.082</v>
+        <v>0.080931</v>
       </c>
       <c r="L401" s="7" t="n">
         <v>131.83</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.02283</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.146</v>
+        <v>-0.145157</v>
       </c>
       <c r="O401" s="7" t="n">
         <v>110.77</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.046</v>
+        <v>-0.046976</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>-0.09</v>
+        <v>-0.08862100000000001</v>
       </c>
     </row>
     <row r="402">
@@ -60304,46 +60304,46 @@
         <v>94.67</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.042</v>
+        <v>-0.040247</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>-0.037</v>
+        <v>-0.036655</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>95.66</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>0.011</v>
+        <v>0.011205</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>0.02</v>
+        <v>0.019164</v>
       </c>
       <c r="I403" s="7" t="n">
         <v>88.31</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.022</v>
+        <v>0.019746</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>0.045</v>
+        <v>0.042644</v>
       </c>
       <c r="L403" s="7" t="n">
         <v>103.75</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>0.001</v>
+        <v>0.003191</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.003</v>
+        <v>-0.002251</v>
       </c>
       <c r="O403" s="7" t="n">
         <v>93.53</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.097</v>
+        <v>-0.094667</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>-0.097</v>
+        <v>-0.09510200000000001</v>
       </c>
     </row>
     <row r="404">
@@ -60359,46 +60359,46 @@
         <v>103.31</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.026</v>
+        <v>-0.024181</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.033</v>
+        <v>-0.032317</v>
       </c>
       <c r="F404" s="6" t="n">
         <v>100.01</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>-0.035</v>
+        <v>-0.032317</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>0</v>
+        <v>0.0009909999999999999</v>
       </c>
       <c r="I404" s="6" t="n">
         <v>95.81999999999999</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.087863</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.006861</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>104.63</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>0.024</v>
+        <v>0.031142</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>0.006</v>
+        <v>0.008671</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>107.13</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.015349</v>
       </c>
       <c r="Q404" s="10" t="n">
-        <v>-0.068</v>
+        <v>-0.06782000000000001</v>
       </c>
     </row>
     <row r="405">
@@ -60414,46 +60414,46 @@
         <v>106.3</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.059</v>
+        <v>0.060349</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.009364000000000001</v>
       </c>
       <c r="F405" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.101</v>
+        <v>0.103364</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.026</v>
+        <v>0.026741</v>
       </c>
       <c r="I405" s="7" t="n">
         <v>108.88</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.185</v>
+        <v>0.18335</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>0.041</v>
+        <v>0.040575</v>
       </c>
       <c r="L405" s="7" t="n">
         <v>108.21</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>0.02</v>
+        <v>0.026368</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.012</v>
+        <v>0.01316</v>
       </c>
       <c r="O405" s="7" t="n">
         <v>103.67</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.013</v>
+        <v>0.012501</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>-0.048</v>
+        <v>-0.048259</v>
       </c>
     </row>
     <row r="406">
@@ -60469,46 +60469,46 @@
         <v>109.02</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.011</v>
+        <v>0.011505</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.005</v>
+        <v>-0.004976</v>
       </c>
       <c r="F406" s="6" t="n">
         <v>111.57</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.027</v>
+        <v>0.026875</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.027</v>
+        <v>0.02677</v>
       </c>
       <c r="I406" s="6" t="n">
         <v>112.31</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>-0.047</v>
+        <v>-0.046847</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>0.019</v>
+        <v>0.019413</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>110.76</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>0.124</v>
+        <v>0.124011</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.034</v>
+        <v>0.034404</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>106.06</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.006557</v>
       </c>
       <c r="Q406" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.039814</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
+++ b/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
@@ -16978,7 +16978,7 @@
         <v>45566</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>109.31</v>
+        <v>113.1</v>
       </c>
       <c r="D387" s="7" t="n">
         <v>103.67</v>
@@ -17021,7 +17021,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>109.8</v>
+        <v>113.7</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>103.33</v>
@@ -17064,7 +17064,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>106.09</v>
+        <v>109.7</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>101.15</v>
@@ -17107,7 +17107,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>105.2</v>
+        <v>107.4</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>100.26</v>
@@ -17150,7 +17150,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>105.94</v>
+        <v>107.3</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>102.49</v>
@@ -17193,7 +17193,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>106.09</v>
+        <v>107.9</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>104.74</v>
@@ -17236,7 +17236,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>102.19</v>
+        <v>105.6</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>99.77</v>
@@ -17279,7 +17279,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>104.55</v>
+        <v>106.8</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>103.92</v>
@@ -17322,7 +17322,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>102.97</v>
+        <v>105.6</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>102.09</v>
@@ -17365,7 +17365,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>104.84</v>
+        <v>107.5</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>101.17</v>
@@ -17408,7 +17408,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>101.93</v>
+        <v>103.9</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>100.13</v>
@@ -17451,7 +17451,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>102.03</v>
+        <v>101</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>98.14</v>
@@ -17494,7 +17494,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>103.03</v>
+        <v>102.2</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>102.34</v>
@@ -17537,7 +17537,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>103.61</v>
+        <v>102.8</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>103.93</v>
@@ -17580,7 +17580,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>104.06</v>
+        <v>103.6</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>104.88</v>
@@ -17623,7 +17623,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>103.02</v>
+        <v>102.3</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>103.85</v>
@@ -17666,7 +17666,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>102.66</v>
+        <v>101.1</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>104.19</v>
@@ -17709,7 +17709,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>103.26</v>
+        <v>102</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>101.99</v>
@@ -17752,7 +17752,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>107.52</v>
+        <v>107.4</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>108.64</v>
@@ -17795,7 +17795,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>107.08</v>
+        <v>107.1</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>106.03</v>
@@ -37520,10 +37520,10 @@
         <v>45566</v>
       </c>
       <c r="C387" s="9" t="n">
-        <v>-0.015048</v>
+        <v>0.001</v>
       </c>
       <c r="D387" s="9" t="n">
-        <v>-0.033766</v>
+        <v>-0.045</v>
       </c>
       <c r="E387" s="9" t="n">
         <v>-0.046713</v>
@@ -37538,10 +37538,10 @@
         <v>0.023313</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>-0.060451</v>
+        <v>-0.035</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.092805</v>
+        <v>-0.163</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>0.000648</v>
@@ -37572,10 +37572,10 @@
         <v>45597</v>
       </c>
       <c r="C388" s="10" t="n">
-        <v>0.004483</v>
+        <v>0.001</v>
       </c>
       <c r="D388" s="10" t="n">
-        <v>-0.00372</v>
+        <v>-0.003</v>
       </c>
       <c r="E388" s="10" t="n">
         <v>-0.00328</v>
@@ -37590,10 +37590,10 @@
         <v>0.047789</v>
       </c>
       <c r="I388" s="10" t="n">
-        <v>0.04592</v>
+        <v>0.068</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>-0.113549</v>
+        <v>-0.148</v>
       </c>
       <c r="K388" s="10" t="n">
         <v>0.057778</v>
@@ -37624,10 +37624,10 @@
         <v>45627</v>
       </c>
       <c r="C389" s="9" t="n">
-        <v>-0.033789</v>
+        <v>-0.026</v>
       </c>
       <c r="D389" s="9" t="n">
-        <v>-0.050054</v>
+        <v>-0.041</v>
       </c>
       <c r="E389" s="9" t="n">
         <v>-0.021097</v>
@@ -37642,10 +37642,10 @@
         <v>-0.006909</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>0.013716</v>
+        <v>0.043</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>-0.150542</v>
+        <v>-0.171</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>-0.018771</v>
@@ -37676,46 +37676,46 @@
         <v>45658</v>
       </c>
       <c r="C390" s="10" t="n">
-        <v>-0.008389000000000001</v>
+        <v>-0.015</v>
       </c>
       <c r="D390" s="10" t="n">
-        <v>-0.064972</v>
+        <v>-0.059</v>
       </c>
       <c r="E390" s="10" t="n">
-        <v>-0.008799</v>
+        <v>-0.014</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>-0.08896</v>
+        <v>-0.09</v>
       </c>
       <c r="G390" s="10" t="n">
-        <v>-0.010079</v>
+        <v>-0.018</v>
       </c>
       <c r="H390" s="10" t="n">
-        <v>-0.034873</v>
+        <v>-0.023</v>
       </c>
       <c r="I390" s="10" t="n">
-        <v>-0.018749</v>
+        <v>-0.014</v>
       </c>
       <c r="J390" s="10" t="n">
-        <v>-0.150955</v>
+        <v>-0.142</v>
       </c>
       <c r="K390" s="10" t="n">
-        <v>-0.06445099999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="L390" s="10" t="n">
-        <v>-0.021894</v>
+        <v>0.022</v>
       </c>
       <c r="M390" s="10" t="n">
-        <v>-0.112933</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="N390" s="10" t="n">
-        <v>-0.016505</v>
+        <v>-0.016</v>
       </c>
       <c r="O390" s="10" t="n">
-        <v>-0.133866</v>
+        <v>-0.136</v>
       </c>
       <c r="P390" s="10" t="n">
-        <v>-0.002183</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="391">
@@ -37728,46 +37728,46 @@
         <v>45689</v>
       </c>
       <c r="C391" s="9" t="n">
-        <v>0.007034</v>
+        <v>0.001</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.057222</v>
+        <v>-0.06</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>0.022242</v>
+        <v>0.017</v>
       </c>
       <c r="F391" s="9" t="n">
-        <v>-0.040805</v>
+        <v>-0.049</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.007209</v>
+        <v>-0.011</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.06690400000000001</v>
+        <v>-0.063</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>0.134879</v>
+        <v>0.128</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>-0.158449</v>
+        <v>-0.168</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>-0.048798</v>
+        <v>-0.021</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>-0.014432</v>
+        <v>0.021</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.083744</v>
+        <v>-0.077</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.080612</v>
+        <v>-0.093</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>-0.07786</v>
+        <v>-0.081</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.080017</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="392">
@@ -37780,46 +37780,46 @@
         <v>45717</v>
       </c>
       <c r="C392" s="10" t="n">
-        <v>0.001416</v>
+        <v>0.003</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.050139</v>
+        <v>-0.047</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>0.021953</v>
+        <v>0.008</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>-0.023403</v>
+        <v>-0.031</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.024142</v>
+        <v>-0.007</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.08501400000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="I392" s="10" t="n">
-        <v>0.165855</v>
+        <v>0.147</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>-0.168667</v>
+        <v>-0.171</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>-0.090119</v>
+        <v>-0.066</v>
       </c>
       <c r="L392" s="10" t="n">
-        <v>-0.12328</v>
+        <v>-0.1</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.045168</v>
+        <v>-0.022</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.082334</v>
+        <v>-0.08</v>
       </c>
       <c r="O392" s="10" t="n">
-        <v>-0.146324</v>
+        <v>-0.148</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.07979700000000001</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="393">
@@ -37832,46 +37832,46 @@
         <v>45748</v>
       </c>
       <c r="C393" s="9" t="n">
-        <v>-0.036761</v>
+        <v>-0.017</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.088891</v>
+        <v>-0.077</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.047451</v>
+        <v>-0.011</v>
       </c>
       <c r="F393" s="9" t="n">
-        <v>-0.073286</v>
+        <v>-0.055</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.020089</v>
+        <v>-0.022</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.096165</v>
+        <v>-0.091</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>-0.005822</v>
+        <v>0.024</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.130797</v>
+        <v>-0.118</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>-0.08361</v>
+        <v>-0.083</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>-0.152479</v>
+        <v>-0.143</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.012811</v>
+        <v>-0.019</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.097068</v>
+        <v>-0.091</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>-0.08448</v>
+        <v>-0.073</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.088647</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="394">
@@ -37884,46 +37884,46 @@
         <v>45778</v>
       </c>
       <c r="C394" s="10" t="n">
-        <v>0.023094</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.06443</v>
+        <v>-0.067</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>0.041596</v>
+        <v>0.014</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>-0.050872</v>
+        <v>-0.05</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>0.001803</v>
+        <v>0</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.077199</v>
+        <v>-0.082</v>
       </c>
       <c r="I394" s="10" t="n">
-        <v>0.086093</v>
+        <v>0.079</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>-0.185542</v>
+        <v>-0.171</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>-0.027668</v>
+        <v>-0.034</v>
       </c>
       <c r="L394" s="10" t="n">
-        <v>-0.06701699999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>0.027527</v>
+        <v>-0.019</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.104474</v>
+        <v>-0.106</v>
       </c>
       <c r="O394" s="10" t="n">
-        <v>-0.258816</v>
+        <v>-0.267</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.073035</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="395">
@@ -37936,46 +37936,46 @@
         <v>45809</v>
       </c>
       <c r="C395" s="9" t="n">
-        <v>-0.015112</v>
+        <v>-0.014</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.072426</v>
+        <v>-0.068</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.01761</v>
+        <v>-0.008</v>
       </c>
       <c r="F395" s="9" t="n">
-        <v>-0.047579</v>
+        <v>-0.033</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.013453</v>
+        <v>-0.016</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.109162</v>
+        <v>-0.114</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>0.127166</v>
+        <v>0.118</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>-0.168133</v>
+        <v>-0.138</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>-0.121275</v>
+        <v>-0.132</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>-0.162111</v>
+        <v>-0.155</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.08884499999999999</v>
+        <v>-0.114</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.096884</v>
+        <v>-0.096</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>-0.141362</v>
+        <v>-0.148</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.083341</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="396">
@@ -37988,46 +37988,46 @@
         <v>45839</v>
       </c>
       <c r="C396" s="10" t="n">
-        <v>0.018161</v>
+        <v>0.016</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.076462</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.009011999999999999</v>
+        <v>-0.013</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>-0.085428</v>
+        <v>-0.075</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>0.041295</v>
+        <v>0.049</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.060399</v>
+        <v>-0.059</v>
       </c>
       <c r="I396" s="10" t="n">
-        <v>0.048605</v>
+        <v>0.046</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>-0.193244</v>
+        <v>-0.176</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>-0.113206</v>
+        <v>-0.114</v>
       </c>
       <c r="L396" s="10" t="n">
-        <v>-0.179896</v>
+        <v>-0.172</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.044993</v>
+        <v>-0.049</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.030429</v>
+        <v>-0.015</v>
       </c>
       <c r="O396" s="10" t="n">
-        <v>-0.049179</v>
+        <v>-0.015</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.02938</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="397">
@@ -38040,46 +38040,46 @@
         <v>45870</v>
       </c>
       <c r="C397" s="9" t="n">
-        <v>-0.027757</v>
+        <v>-0.027</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.09371400000000001</v>
+        <v>-0.089</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.01028</v>
+        <v>-0.015</v>
       </c>
       <c r="F397" s="9" t="n">
-        <v>-0.06977</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.038642</v>
+        <v>-0.031</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.11661</v>
+        <v>-0.105</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>0.114345</v>
+        <v>0.1</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>-0.193146</v>
+        <v>-0.185</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>-0.125056</v>
+        <v>-0.092</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>-0.136875</v>
+        <v>-0.123</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.12077</v>
+        <v>-0.056</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.11674</v>
+        <v>-0.119</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>-0.153669</v>
+        <v>-0.154</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.105321</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="398">
@@ -38092,46 +38092,46 @@
         <v>45901</v>
       </c>
       <c r="C398" s="10" t="n">
-        <v>0.0009810000000000001</v>
+        <v>-0.003</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.08064499999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.019874</v>
+        <v>-0.026</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>-0.097563</v>
+        <v>-0.102</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>0.01698</v>
+        <v>0.019</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.06492000000000001</v>
+        <v>-0.061</v>
       </c>
       <c r="I398" s="10" t="n">
-        <v>-0.013778</v>
+        <v>-0.02</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.163115</v>
+        <v>-0.164</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>-0.110615</v>
+        <v>-0.106</v>
       </c>
       <c r="L398" s="10" t="n">
-        <v>-0.171639</v>
+        <v>-0.168</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.045442</v>
+        <v>-0.04</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.033193</v>
+        <v>-0.033</v>
       </c>
       <c r="O398" s="10" t="n">
-        <v>-0.158983</v>
+        <v>-0.164</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.006402</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="399">
@@ -38144,46 +38144,46 @@
         <v>45931</v>
       </c>
       <c r="C399" s="9" t="n">
-        <v>0.009801000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.057451</v>
+        <v>-0.058</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>0.042796</v>
+        <v>0.039</v>
       </c>
       <c r="F399" s="9" t="n">
-        <v>-0.012829</v>
+        <v>-0.016</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.023394</v>
+        <v>-0.022</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.106576</v>
+        <v>-0.103</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>0.123451</v>
+        <v>0.118</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>-0.120576</v>
+        <v>-0.126</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>-0.121106</v>
+        <v>-0.118</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>-0.17199</v>
+        <v>-0.171</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.052782</v>
+        <v>-0.047</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.095293</v>
+        <v>-0.094</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>-0.128501</v>
+        <v>-0.132</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.089837</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -38196,46 +38196,46 @@
         <v>45962</v>
       </c>
       <c r="C400" s="10" t="n">
-        <v>0.005629</v>
+        <v>0.004</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.056375</v>
+        <v>-0.057</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>0.015536</v>
+        <v>0.015</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>0.005807</v>
+        <v>0.006</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>-0.000386</v>
+        <v>-0.002</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.117732</v>
+        <v>-0.116</v>
       </c>
       <c r="I400" s="10" t="n">
-        <v>0.09221</v>
+        <v>0.092</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>-0.06801500000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>-0.153805</v>
+        <v>-0.152</v>
       </c>
       <c r="L400" s="10" t="n">
-        <v>-0.191459</v>
+        <v>-0.187</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.103646</v>
+        <v>-0.101</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.090767</v>
+        <v>-0.091</v>
       </c>
       <c r="O400" s="10" t="n">
-        <v>-0.186943</v>
+        <v>-0.191</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.077817</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="401">
@@ -38248,46 +38248,46 @@
         <v>45992</v>
       </c>
       <c r="C401" s="9" t="n">
-        <v>0.004343</v>
+        <v>0.005</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.019135</v>
+        <v>-0.016</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>0.009141</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F401" s="9" t="n">
-        <v>0.036876</v>
+        <v>0.041</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>-0.001546</v>
+        <v>-0.003</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.078316</v>
+        <v>-0.079</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>0.139663</v>
+        <v>0.142</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>-0.032787</v>
+        <v>-0.03</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>-0.118588</v>
+        <v>-0.118</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>-0.165981</v>
+        <v>-0.163</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.054836</v>
+        <v>-0.053</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.048774</v>
+        <v>-0.049</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>-0.034135</v>
+        <v>-0.027</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.049122</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="402">
@@ -38300,46 +38300,46 @@
         <v>46023</v>
       </c>
       <c r="C402" s="10" t="n">
-        <v>-0.009993999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="D402" s="10" t="n">
-        <v>-0.020722</v>
+        <v>-0.022</v>
       </c>
       <c r="E402" s="10" t="n">
-        <v>-0.009821</v>
+        <v>-0.008</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>0.035807</v>
+        <v>0.038</v>
       </c>
       <c r="G402" s="10" t="n">
-        <v>-0.006871</v>
+        <v>-0.011</v>
       </c>
       <c r="H402" s="10" t="n">
-        <v>-0.07532899999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="I402" s="10" t="n">
-        <v>0.077316</v>
+        <v>0.079</v>
       </c>
       <c r="J402" s="10" t="n">
-        <v>-0.000807</v>
+        <v>0</v>
       </c>
       <c r="K402" s="10" t="n">
-        <v>-0.107851</v>
+        <v>-0.111</v>
       </c>
       <c r="L402" s="10" t="n">
-        <v>-0.141022</v>
+        <v>-0.133</v>
       </c>
       <c r="M402" s="10" t="n">
-        <v>-0.07845100000000001</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="N402" s="10" t="n">
-        <v>-0.048812</v>
+        <v>-0.052</v>
       </c>
       <c r="O402" s="10" t="n">
-        <v>-0.038568</v>
+        <v>-0.036</v>
       </c>
       <c r="P402" s="10" t="n">
-        <v>-0.058026</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="403">
@@ -38352,46 +38352,46 @@
         <v>46054</v>
       </c>
       <c r="C403" s="9" t="n">
-        <v>-0.003494</v>
+        <v>-0.008</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.030961</v>
+        <v>-0.036</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>0.003274</v>
+        <v>0.001</v>
       </c>
       <c r="F403" s="9" t="n">
-        <v>0.016587</v>
+        <v>0.015</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>-0.015299</v>
+        <v>-0.023</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>-0.08286399999999999</v>
+        <v>-0.091</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>0.017306</v>
+        <v>0.018</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.014874</v>
+        <v>0.01</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>-0.12758</v>
+        <v>-0.136</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>-0.193103</v>
+        <v>-0.193</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>-0.059824</v>
+        <v>-0.075</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.05111</v>
+        <v>-0.057</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>-0.148554</v>
+        <v>-0.149</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.037107</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="404">
@@ -38404,46 +38404,46 @@
         <v>46082</v>
       </c>
       <c r="C404" s="10" t="n">
-        <v>0.005845</v>
+        <v>0.004</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.026675</v>
+        <v>-0.031</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.021115</v>
+        <v>-0.024</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>-0.026255</v>
+        <v>-0.032</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>0.03236</v>
+        <v>0.031</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>-0.029762</v>
+        <v>-0.032</v>
       </c>
       <c r="I404" s="10" t="n">
-        <v>-0.08277</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>0.03482</v>
+        <v>0.024</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.073404</v>
+        <v>-0.073</v>
       </c>
       <c r="L404" s="10" t="n">
-        <v>-0.129176</v>
+        <v>-0.131</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>-0.017345</v>
+        <v>-0.015</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>-0.01184</v>
+        <v>-0.016</v>
       </c>
       <c r="O404" s="10" t="n">
-        <v>0.06449199999999999</v>
+        <v>0.064</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.016874</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="405">
@@ -38456,46 +38456,46 @@
         <v>46113</v>
       </c>
       <c r="C405" s="9" t="n">
-        <v>0.041255</v>
+        <v>0.04</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.052158</v>
+        <v>0.051</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>0.065202</v>
+        <v>0.065</v>
       </c>
       <c r="F405" s="9" t="n">
-        <v>0.088904</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.021377</v>
+        <v>0.02</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.011295</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>0.163739</v>
+        <v>0.167</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.022021</v>
+        <v>0.011</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>-0.102228</v>
+        <v>-0.106</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>-0.078404</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>-0.122099</v>
+        <v>-0.124</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.08785800000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>-0.01331</v>
+        <v>-0.011</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.100659</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="406">
@@ -38508,46 +38508,46 @@
         <v>46143</v>
       </c>
       <c r="C406" s="10" t="n">
-        <v>-0.004092</v>
+        <v>-0.004</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.024199</v>
+        <v>0.024</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.024024</v>
+        <v>-0.024</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>0.020304</v>
+        <v>0.02</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.015392</v>
+        <v>0.015</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.025012</v>
+        <v>0.025</v>
       </c>
       <c r="I406" s="10" t="n">
-        <v>-0.054435</v>
+        <v>-0.054</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>0.117552</v>
+        <v>0.118</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>-0.077236</v>
+        <v>-0.077</v>
       </c>
       <c r="L406" s="10" t="n">
-        <v>-0.049835</v>
+        <v>-0.05</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>-0.09073100000000001</v>
+        <v>-0.091</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.08930399999999999</v>
+        <v>0.089</v>
       </c>
       <c r="O406" s="10" t="n">
-        <v>0.071329</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>0.09743300000000001</v>
+        <v>0.097</v>
       </c>
     </row>
   </sheetData>
@@ -59442,19 +59442,19 @@
         <v>91.53</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.045966</v>
+        <v>-0.029</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>0.03116</v>
+        <v>0.047</v>
       </c>
       <c r="L387" s="7" t="n">
         <v>125.59</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>-0.095564</v>
+        <v>-0.166</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>0.089361</v>
+        <v>0.034</v>
       </c>
       <c r="O387" s="7" t="n">
         <v>121.97</v>
@@ -59497,19 +59497,19 @@
         <v>97.25</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>0.059599</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K388" s="10" t="n">
-        <v>0.033895</v>
+        <v>0.049</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>124.25</v>
       </c>
       <c r="M388" s="10" t="n">
-        <v>-0.111421</v>
+        <v>-0.147</v>
       </c>
       <c r="N388" s="10" t="n">
-        <v>0.067721</v>
+        <v>0.014</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>121.22</v>
@@ -59552,19 +59552,19 @@
         <v>83.88</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>0.001074</v>
+        <v>0.032</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>0.031246</v>
+        <v>0.048</v>
       </c>
       <c r="L389" s="7" t="n">
         <v>134.91</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>-0.135026</v>
+        <v>-0.164</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>0.045963</v>
+        <v>-0.004</v>
       </c>
       <c r="O389" s="7" t="n">
         <v>116.23</v>
@@ -59644,46 +59644,46 @@
         <v>98.64</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.080022</v>
+        <v>-0.078</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>-0.077477</v>
+        <v>-0.074</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.046755</v>
+        <v>-0.052</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.07618</v>
+        <v>-0.079</v>
       </c>
       <c r="I391" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>0.140825</v>
+        <v>0.141</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>0.050031</v>
+        <v>0.056</v>
       </c>
       <c r="L391" s="7" t="n">
         <v>103.42</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.17211</v>
+        <v>-0.18</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.166833</v>
+        <v>-0.174</v>
       </c>
       <c r="O391" s="7" t="n">
         <v>103.31</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.113067</v>
+        <v>-0.104</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>-0.078884</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="392">
@@ -59699,46 +59699,46 @@
         <v>105.87</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.005915</v>
+        <v>-0.002</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>-0.053793</v>
+        <v>-0.049</v>
       </c>
       <c r="F392" s="6" t="n">
         <v>103.35</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>0.001356</v>
+        <v>-0.001</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.050219</v>
+        <v>-0.05</v>
       </c>
       <c r="I392" s="6" t="n">
         <v>105.05</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>0.204564</v>
+        <v>0.205</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>0.103742</v>
+        <v>0.108</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>101.47</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.160156</v>
+        <v>-0.159</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.164661</v>
+        <v>-0.164</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>108.8</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.013689</v>
+        <v>-0.004</v>
       </c>
       <c r="Q392" s="10" t="n">
-        <v>-0.057574</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="393">
@@ -59754,46 +59754,46 @@
         <v>100.25</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.131809</v>
+        <v>-0.125</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.074395</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>98.39</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.100886</v>
+        <v>-0.092</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.06349399999999999</v>
+        <v>-0.061</v>
       </c>
       <c r="I393" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.048008</v>
+        <v>-0.037</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>0.061543</v>
+        <v>0.067</v>
       </c>
       <c r="L393" s="7" t="n">
         <v>105.43</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.146316</v>
+        <v>-0.139</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.160082</v>
+        <v>-0.158</v>
       </c>
       <c r="O393" s="7" t="n">
         <v>102.39</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.16389</v>
+        <v>-0.16</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>-0.085881</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="394">
@@ -59809,46 +59809,46 @@
         <v>107.78</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.06594999999999999</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>-0.072632</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F394" s="6" t="n">
         <v>108.65</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>-0.041634</v>
+        <v>-0.043</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.058827</v>
+        <v>-0.058</v>
       </c>
       <c r="I394" s="6" t="n">
         <v>117.83</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>0.102451</v>
+        <v>0.096</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>0.07116500000000001</v>
+        <v>0.074</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.182241</v>
+        <v>-0.175</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.164421</v>
+        <v>-0.162</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>106.76</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.093179</v>
+        <v>-0.103</v>
       </c>
       <c r="Q394" s="10" t="n">
-        <v>-0.087368</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="395">
@@ -59864,46 +59864,46 @@
         <v>98.92</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.068023</v>
+        <v>-0.064</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.07188899999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.04444</v>
+        <v>-0.032</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.05654</v>
+        <v>-0.054</v>
       </c>
       <c r="I395" s="7" t="n">
         <v>87.73999999999999</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>0.127039</v>
+        <v>0.12</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>0.079336</v>
+        <v>0.082</v>
       </c>
       <c r="L395" s="7" t="n">
         <v>104.88</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.161966</v>
+        <v>-0.137</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.164006</v>
+        <v>-0.159</v>
       </c>
       <c r="O395" s="7" t="n">
         <v>102.41</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.092432</v>
+        <v>-0.097</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>-0.088196</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="396">
@@ -59919,46 +59919,46 @@
         <v>106.74</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.068993</v>
+        <v>-0.066</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.07146</v>
+        <v>-0.068</v>
       </c>
       <c r="F396" s="6" t="n">
         <v>102.77</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>-0.078957</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.059907</v>
+        <v>-0.057</v>
       </c>
       <c r="I396" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>0.058786</v>
+        <v>0.055</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>0.076241</v>
+        <v>0.078</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>105.87</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.188611</v>
+        <v>-0.172</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.167692</v>
+        <v>-0.161</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>111.33</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.058122</v>
+        <v>-0.059</v>
       </c>
       <c r="Q396" s="10" t="n">
-        <v>-0.0838</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="397">
@@ -59974,46 +59974,46 @@
         <v>102.22</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.110434</v>
+        <v>-0.104</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.076501</v>
+        <v>-0.073</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>101.61</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.07391499999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.061709</v>
+        <v>-0.059</v>
       </c>
       <c r="I397" s="7" t="n">
         <v>91.92</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>0.09912700000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>0.07893500000000001</v>
+        <v>0.079</v>
       </c>
       <c r="L397" s="7" t="n">
         <v>112.27</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.189094</v>
+        <v>-0.179</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.170628</v>
+        <v>-0.164</v>
       </c>
       <c r="O397" s="7" t="n">
         <v>102.94</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.148693</v>
+        <v>-0.137</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>-0.092241</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="398">
@@ -60029,46 +60029,46 @@
         <v>99.59</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.067247</v>
+        <v>-0.067</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.07550800000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="F398" s="6" t="n">
         <v>94.42</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>-0.10832</v>
+        <v>-0.106</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.066858</v>
+        <v>-0.067</v>
       </c>
       <c r="I398" s="6" t="n">
         <v>85.19</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.028288</v>
+        <v>-0.031</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>0.06715500000000001</v>
+        <v>0.067</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>104.59</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.169591</v>
+        <v>-0.163</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.170513</v>
+        <v>-0.171</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>105.57</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.020596</v>
+        <v>-0.024</v>
       </c>
       <c r="Q398" s="10" t="n">
-        <v>-0.084797</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="399">
@@ -60084,46 +60084,46 @@
         <v>107.9</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.056241</v>
+        <v>-0.055</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>-0.07352300000000001</v>
+        <v>-0.074</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.008817999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.060994</v>
+        <v>-0.061</v>
       </c>
       <c r="I399" s="7" t="n">
         <v>103.82</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>0.134273</v>
+        <v>0.135</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>0.074062</v>
+        <v>0.074</v>
       </c>
       <c r="L399" s="7" t="n">
         <v>110.07</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.123577</v>
+        <v>-0.122</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.165838</v>
+        <v>-0.167</v>
       </c>
       <c r="O399" s="7" t="n">
         <v>109.17</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.104944</v>
+        <v>-0.105</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>-0.08691599999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -60139,46 +60139,46 @@
         <v>107.74</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.065163</v>
+        <v>-0.064</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>-0.072736</v>
+        <v>-0.073</v>
       </c>
       <c r="F400" s="6" t="n">
         <v>111.27</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>0.010627</v>
+        <v>0.013</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.054291</v>
+        <v>-0.054</v>
       </c>
       <c r="I400" s="6" t="n">
         <v>107.18</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>0.102108</v>
+        <v>0.103</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>0.07682600000000001</v>
+        <v>0.077</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>115.79</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.068089</v>
+        <v>-0.065</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.15707</v>
+        <v>-0.158</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>103.66</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.144861</v>
+        <v>-0.145</v>
       </c>
       <c r="Q400" s="10" t="n">
-        <v>-0.092401</v>
+        <v>-0.093</v>
       </c>
     </row>
     <row r="401">
@@ -60194,46 +60194,46 @@
         <v>111.63</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.002413</v>
+        <v>0</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>-0.06684900000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>112.38</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>0.03892</v>
+        <v>0.043</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.046442</v>
+        <v>-0.046</v>
       </c>
       <c r="I401" s="7" t="n">
         <v>94.72</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>0.129232</v>
+        <v>0.133</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>0.080931</v>
+        <v>0.082</v>
       </c>
       <c r="L401" s="7" t="n">
         <v>131.83</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.02283</v>
+        <v>-0.019</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.145157</v>
+        <v>-0.146</v>
       </c>
       <c r="O401" s="7" t="n">
         <v>110.77</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.046976</v>
+        <v>-0.046</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>-0.08862100000000001</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="402">
@@ -60304,46 +60304,46 @@
         <v>94.67</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.040247</v>
+        <v>-0.042</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>-0.036655</v>
+        <v>-0.037</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>95.66</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>0.011205</v>
+        <v>0.011</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>0.019164</v>
+        <v>0.02</v>
       </c>
       <c r="I403" s="7" t="n">
         <v>88.31</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.019746</v>
+        <v>0.022</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>0.042644</v>
+        <v>0.045</v>
       </c>
       <c r="L403" s="7" t="n">
         <v>103.75</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>0.003191</v>
+        <v>0.001</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.002251</v>
+        <v>-0.003</v>
       </c>
       <c r="O403" s="7" t="n">
         <v>93.53</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.094667</v>
+        <v>-0.097</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>-0.09510200000000001</v>
+        <v>-0.097</v>
       </c>
     </row>
     <row r="404">
@@ -60359,46 +60359,46 @@
         <v>103.31</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.024181</v>
+        <v>-0.026</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.032317</v>
+        <v>-0.033</v>
       </c>
       <c r="F404" s="6" t="n">
         <v>100.01</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>-0.032317</v>
+        <v>-0.035</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>0.0009909999999999999</v>
+        <v>0</v>
       </c>
       <c r="I404" s="6" t="n">
         <v>95.81999999999999</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>-0.087863</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.006861</v>
+        <v>-0.007</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>104.63</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>0.031142</v>
+        <v>0.024</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>0.008671</v>
+        <v>0.006</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>107.13</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.015349</v>
+        <v>-0.015</v>
       </c>
       <c r="Q404" s="10" t="n">
-        <v>-0.06782000000000001</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="405">
@@ -60414,46 +60414,46 @@
         <v>106.3</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.060349</v>
+        <v>0.059</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>-0.009364000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F405" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.103364</v>
+        <v>0.101</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.026741</v>
+        <v>0.026</v>
       </c>
       <c r="I405" s="7" t="n">
         <v>108.88</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.18335</v>
+        <v>0.185</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>0.040575</v>
+        <v>0.041</v>
       </c>
       <c r="L405" s="7" t="n">
         <v>108.21</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>0.026368</v>
+        <v>0.02</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.01316</v>
+        <v>0.012</v>
       </c>
       <c r="O405" s="7" t="n">
         <v>103.67</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.012501</v>
+        <v>0.013</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>-0.048259</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="406">
@@ -60469,46 +60469,46 @@
         <v>109.02</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.011505</v>
+        <v>0.011</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.004976</v>
+        <v>-0.005</v>
       </c>
       <c r="F406" s="6" t="n">
         <v>111.57</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.026875</v>
+        <v>0.027</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.02677</v>
+        <v>0.027</v>
       </c>
       <c r="I406" s="6" t="n">
         <v>112.31</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>-0.046847</v>
+        <v>-0.047</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>0.019413</v>
+        <v>0.019</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>110.76</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>0.124011</v>
+        <v>0.124</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.034404</v>
+        <v>0.034</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>106.06</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>-0.006557</v>
+        <v>-0.007</v>
       </c>
       <c r="Q406" s="10" t="n">
-        <v>-0.039814</v>
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
+++ b/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
         <v>45566</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>109.27</v>
+        <v>113.1</v>
       </c>
       <c r="D387" s="7" t="n">
         <v>103.61</v>
@@ -17021,7 +17021,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>109.76</v>
+        <v>113.7</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>103.29</v>
@@ -17064,7 +17064,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>106.07</v>
+        <v>109.7</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>101.15</v>
@@ -17107,7 +17107,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>105.19</v>
+        <v>107.4</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>100.33</v>
@@ -17150,7 +17150,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>105.99</v>
+        <v>107.3</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>102.63</v>
@@ -17193,7 +17193,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>106.18</v>
+        <v>107.9</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>104.96</v>
@@ -17236,7 +17236,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>102.33</v>
+        <v>105.6</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>100.09</v>
@@ -17279,7 +17279,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>104.78</v>
+        <v>106.8</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>104.43</v>
@@ -17322,7 +17322,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>102.7</v>
+        <v>105.6</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>101.29</v>
@@ -17365,7 +17365,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>104.79</v>
+        <v>107.5</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>100.96</v>
@@ -17408,7 +17408,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>101.9</v>
+        <v>103.9</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>99.98</v>
@@ -17451,7 +17451,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>101.99</v>
+        <v>101</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>98.02</v>
@@ -17494,7 +17494,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>102.99</v>
+        <v>102.2</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>102.27</v>
@@ -17537,7 +17537,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>103.57</v>
+        <v>102.8</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>103.89</v>
@@ -17580,7 +17580,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>104.02</v>
+        <v>103.6</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>104.89</v>
@@ -17623,7 +17623,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>103.06</v>
+        <v>102.3</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>103.93</v>
@@ -17666,7 +17666,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>102.7</v>
+        <v>101.1</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>104.36</v>
@@ -17709,7 +17709,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>103.36</v>
+        <v>102</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>102.24</v>
@@ -17752,7 +17752,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>107.77</v>
+        <v>107.4</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>109.18</v>
@@ -17795,7 +17795,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>107.29</v>
+        <v>107.1</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>106.47</v>
@@ -17838,7 +17838,7 @@
         <v>46174</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>108.74</v>
+        <v>108.7</v>
       </c>
       <c r="D407" s="7" t="n">
         <v>110.24</v>
@@ -17918,7 +17918,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -37563,10 +37563,10 @@
         <v>45566</v>
       </c>
       <c r="C387" s="9" t="n">
-        <v>-0.015231</v>
+        <v>0.001</v>
       </c>
       <c r="D387" s="9" t="n">
-        <v>-0.033864</v>
+        <v>-0.045</v>
       </c>
       <c r="E387" s="9" t="n">
         <v>-0.046387</v>
@@ -37581,10 +37581,10 @@
         <v>0.023488</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>-0.060137</v>
+        <v>-0.035</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.092969</v>
+        <v>-0.163</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>0.000555</v>
@@ -37615,10 +37615,10 @@
         <v>45597</v>
       </c>
       <c r="C388" s="10" t="n">
-        <v>0.004484</v>
+        <v>0.001</v>
       </c>
       <c r="D388" s="10" t="n">
-        <v>-0.003993</v>
+        <v>-0.003</v>
       </c>
       <c r="E388" s="10" t="n">
         <v>-0.003089</v>
@@ -37633,10 +37633,10 @@
         <v>0.047964</v>
       </c>
       <c r="I388" s="10" t="n">
-        <v>0.046145</v>
+        <v>0.068</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>-0.11381</v>
+        <v>-0.148</v>
       </c>
       <c r="K388" s="10" t="n">
         <v>0.057398</v>
@@ -37667,10 +37667,10 @@
         <v>45627</v>
       </c>
       <c r="C389" s="9" t="n">
-        <v>-0.033619</v>
+        <v>-0.026</v>
       </c>
       <c r="D389" s="9" t="n">
-        <v>-0.050233</v>
+        <v>-0.041</v>
       </c>
       <c r="E389" s="9" t="n">
         <v>-0.020718</v>
@@ -37685,10 +37685,10 @@
         <v>-0.006644</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>0.013939</v>
+        <v>0.043</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>-0.150682</v>
+        <v>-0.171</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>-0.018671</v>
@@ -37719,46 +37719,46 @@
         <v>45658</v>
       </c>
       <c r="C390" s="10" t="n">
-        <v>-0.008296</v>
+        <v>-0.015</v>
       </c>
       <c r="D390" s="10" t="n">
-        <v>-0.06506099999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="E390" s="10" t="n">
-        <v>-0.008107</v>
+        <v>-0.014</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>-0.088738</v>
+        <v>-0.09</v>
       </c>
       <c r="G390" s="10" t="n">
-        <v>-0.01079</v>
+        <v>-0.018</v>
       </c>
       <c r="H390" s="10" t="n">
-        <v>-0.03514</v>
+        <v>-0.023</v>
       </c>
       <c r="I390" s="10" t="n">
-        <v>-0.017972</v>
+        <v>-0.014</v>
       </c>
       <c r="J390" s="10" t="n">
-        <v>-0.151065</v>
+        <v>-0.142</v>
       </c>
       <c r="K390" s="10" t="n">
-        <v>-0.06428499999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="L390" s="10" t="n">
-        <v>-0.021327</v>
+        <v>0.022</v>
       </c>
       <c r="M390" s="10" t="n">
-        <v>-0.113759</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="N390" s="10" t="n">
-        <v>-0.017595</v>
+        <v>-0.016</v>
       </c>
       <c r="O390" s="10" t="n">
-        <v>-0.132904</v>
+        <v>-0.136</v>
       </c>
       <c r="P390" s="10" t="n">
-        <v>-0.003057</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="391">
@@ -37771,46 +37771,46 @@
         <v>45689</v>
       </c>
       <c r="C391" s="9" t="n">
-        <v>0.007605</v>
+        <v>0.001</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.057028</v>
+        <v>-0.06</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>0.022924</v>
+        <v>0.017</v>
       </c>
       <c r="F391" s="9" t="n">
-        <v>-0.040393</v>
+        <v>-0.049</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.006851</v>
+        <v>-0.011</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.06683</v>
+        <v>-0.063</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>0.136052</v>
+        <v>0.128</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>-0.158461</v>
+        <v>-0.168</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>-0.048012</v>
+        <v>-0.021</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>-0.013586</v>
+        <v>0.021</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.083468</v>
+        <v>-0.077</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.081163</v>
+        <v>-0.093</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>-0.076588</v>
+        <v>-0.081</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.08068699999999999</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="392">
@@ -37823,46 +37823,46 @@
         <v>45717</v>
       </c>
       <c r="C392" s="10" t="n">
-        <v>0.001793</v>
+        <v>0.003</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.049843</v>
+        <v>-0.047</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>0.022703</v>
+        <v>0.008</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>-0.022719</v>
+        <v>-0.031</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.024235</v>
+        <v>-0.007</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.08502899999999999</v>
+        <v>-0.075</v>
       </c>
       <c r="I392" s="10" t="n">
-        <v>0.166975</v>
+        <v>0.147</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>-0.168503</v>
+        <v>-0.171</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>-0.089406</v>
+        <v>-0.066</v>
       </c>
       <c r="L392" s="10" t="n">
-        <v>-0.122053</v>
+        <v>-0.1</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.045061</v>
+        <v>-0.022</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.083105</v>
+        <v>-0.08</v>
       </c>
       <c r="O392" s="10" t="n">
-        <v>-0.144005</v>
+        <v>-0.148</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.080719</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="393">
@@ -37875,46 +37875,46 @@
         <v>45748</v>
       </c>
       <c r="C393" s="9" t="n">
-        <v>-0.036259</v>
+        <v>-0.017</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.088212</v>
+        <v>-0.077</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.046399</v>
+        <v>-0.011</v>
       </c>
       <c r="F393" s="9" t="n">
-        <v>-0.071866</v>
+        <v>-0.055</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.020465</v>
+        <v>-0.022</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.096525</v>
+        <v>-0.091</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>-0.004026</v>
+        <v>0.024</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.1306</v>
+        <v>-0.118</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>-0.08184900000000001</v>
+        <v>-0.083</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>-0.150113</v>
+        <v>-0.143</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.012903</v>
+        <v>-0.019</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.098775</v>
+        <v>-0.091</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>-0.081743</v>
+        <v>-0.073</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.091323</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="394">
@@ -37927,46 +37927,46 @@
         <v>45778</v>
       </c>
       <c r="C394" s="10" t="n">
-        <v>0.023942</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.063628</v>
+        <v>-0.067</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>0.043361</v>
+        <v>0.014</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>-0.048994</v>
+        <v>-0.05</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>0.001519</v>
+        <v>0</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.077663</v>
+        <v>-0.082</v>
       </c>
       <c r="I394" s="10" t="n">
-        <v>0.087355</v>
+        <v>0.079</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>-0.184172</v>
+        <v>-0.171</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>-0.025784</v>
+        <v>-0.034</v>
       </c>
       <c r="L394" s="10" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.055</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>0.027141</v>
+        <v>-0.019</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.105678</v>
+        <v>-0.106</v>
       </c>
       <c r="O394" s="10" t="n">
-        <v>-0.255997</v>
+        <v>-0.267</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.07587099999999999</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="395">
@@ -37979,46 +37979,46 @@
         <v>45809</v>
       </c>
       <c r="C395" s="9" t="n">
-        <v>-0.019851</v>
+        <v>-0.014</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.073439</v>
+        <v>-0.068</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.030068</v>
+        <v>-0.008</v>
       </c>
       <c r="F395" s="9" t="n">
-        <v>-0.050614</v>
+        <v>-0.033</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.011474</v>
+        <v>-0.016</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.108593</v>
+        <v>-0.114</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>0.120577</v>
+        <v>0.118</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>-0.169159</v>
+        <v>-0.138</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>-0.125315</v>
+        <v>-0.132</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>-0.165292</v>
+        <v>-0.155</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.088338</v>
+        <v>-0.114</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.09321500000000001</v>
+        <v>-0.096</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>-0.151315</v>
+        <v>-0.148</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.078399</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="396">
@@ -38031,46 +38031,46 @@
         <v>45839</v>
       </c>
       <c r="C396" s="10" t="n">
-        <v>0.020351</v>
+        <v>0.016</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.07649599999999999</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.003258</v>
+        <v>-0.013</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>-0.086252</v>
+        <v>-0.075</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>0.040096</v>
+        <v>0.049</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.060399</v>
+        <v>-0.059</v>
       </c>
       <c r="I396" s="10" t="n">
-        <v>0.048097</v>
+        <v>0.046</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>-0.193215</v>
+        <v>-0.176</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>-0.113547</v>
+        <v>-0.114</v>
       </c>
       <c r="L396" s="10" t="n">
-        <v>-0.180201</v>
+        <v>-0.172</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.045172</v>
+        <v>-0.049</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.030134</v>
+        <v>-0.015</v>
       </c>
       <c r="O396" s="10" t="n">
-        <v>-0.050938</v>
+        <v>-0.015</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.028977</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="397">
@@ -38083,46 +38083,46 @@
         <v>45870</v>
       </c>
       <c r="C397" s="9" t="n">
-        <v>-0.027579</v>
+        <v>-0.027</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.09365800000000001</v>
+        <v>-0.089</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.009707</v>
+        <v>-0.015</v>
       </c>
       <c r="F397" s="9" t="n">
-        <v>-0.07012599999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.038642</v>
+        <v>-0.031</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.116685</v>
+        <v>-0.105</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>0.113731</v>
+        <v>0.1</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>-0.193116</v>
+        <v>-0.185</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>-0.125123</v>
+        <v>-0.092</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>-0.136581</v>
+        <v>-0.123</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.120682</v>
+        <v>-0.056</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.116669</v>
+        <v>-0.119</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>-0.152947</v>
+        <v>-0.154</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.105424</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="398">
@@ -38135,46 +38135,46 @@
         <v>45901</v>
       </c>
       <c r="C398" s="10" t="n">
-        <v>0.000883</v>
+        <v>-0.003</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.08084</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.019604</v>
+        <v>-0.026</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>-0.09783699999999999</v>
+        <v>-0.102</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>0.017076</v>
+        <v>0.019</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.064914</v>
+        <v>-0.061</v>
       </c>
       <c r="I398" s="10" t="n">
-        <v>-0.014319</v>
+        <v>-0.02</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.163128</v>
+        <v>-0.164</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>-0.111293</v>
+        <v>-0.106</v>
       </c>
       <c r="L398" s="10" t="n">
-        <v>-0.173014</v>
+        <v>-0.168</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.045612</v>
+        <v>-0.04</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.032397</v>
+        <v>-0.033</v>
       </c>
       <c r="O398" s="10" t="n">
-        <v>-0.159101</v>
+        <v>-0.164</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.005226</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="399">
@@ -38187,46 +38187,46 @@
         <v>45931</v>
       </c>
       <c r="C399" s="9" t="n">
-        <v>0.009804999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.057472</v>
+        <v>-0.058</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>0.043358</v>
+        <v>0.039</v>
       </c>
       <c r="F399" s="9" t="n">
-        <v>-0.012933</v>
+        <v>-0.016</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.023109</v>
+        <v>-0.022</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.106462</v>
+        <v>-0.103</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>0.123878</v>
+        <v>0.118</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>-0.120615</v>
+        <v>-0.126</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>-0.120803</v>
+        <v>-0.118</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>-0.172389</v>
+        <v>-0.171</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.052672</v>
+        <v>-0.047</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.095438</v>
+        <v>-0.094</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>-0.128135</v>
+        <v>-0.132</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.089714</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -38239,46 +38239,46 @@
         <v>45962</v>
       </c>
       <c r="C400" s="10" t="n">
-        <v>0.005632</v>
+        <v>0.004</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.056396</v>
+        <v>-0.057</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>0.01584</v>
+        <v>0.015</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>0.005809</v>
+        <v>0.006</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>-0.000386</v>
+        <v>-0.002</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.117617</v>
+        <v>-0.116</v>
       </c>
       <c r="I400" s="10" t="n">
-        <v>0.09261900000000001</v>
+        <v>0.092</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>-0.06814099999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>-0.153321</v>
+        <v>-0.152</v>
       </c>
       <c r="L400" s="10" t="n">
-        <v>-0.191233</v>
+        <v>-0.187</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.103515</v>
+        <v>-0.101</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.09116299999999999</v>
+        <v>-0.091</v>
       </c>
       <c r="O400" s="10" t="n">
-        <v>-0.187012</v>
+        <v>-0.191</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.078113</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="401">
@@ -38291,46 +38291,46 @@
         <v>45992</v>
       </c>
       <c r="C401" s="9" t="n">
-        <v>0.004345</v>
+        <v>0.005</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.019327</v>
+        <v>-0.016</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>0.009625999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F401" s="9" t="n">
-        <v>0.036975</v>
+        <v>0.041</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>-0.001449</v>
+        <v>-0.003</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.07811700000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>0.140108</v>
+        <v>0.142</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>-0.032893</v>
+        <v>-0.03</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>-0.118436</v>
+        <v>-0.118</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>-0.166199</v>
+        <v>-0.163</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.05462</v>
+        <v>-0.053</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.048424</v>
+        <v>-0.049</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>-0.033469</v>
+        <v>-0.027</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.048545</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="402">
@@ -38343,46 +38343,46 @@
         <v>46023</v>
       </c>
       <c r="C402" s="10" t="n">
-        <v>-0.009228999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="D402" s="10" t="n">
-        <v>-0.020249</v>
+        <v>-0.022</v>
       </c>
       <c r="E402" s="10" t="n">
-        <v>-0.009152</v>
+        <v>-0.008</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>0.035882</v>
+        <v>0.038</v>
       </c>
       <c r="G402" s="10" t="n">
-        <v>-0.006191</v>
+        <v>-0.011</v>
       </c>
       <c r="H402" s="10" t="n">
-        <v>-0.07383000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="I402" s="10" t="n">
-        <v>0.078083</v>
+        <v>0.079</v>
       </c>
       <c r="J402" s="10" t="n">
-        <v>-0.001165</v>
+        <v>0</v>
       </c>
       <c r="K402" s="10" t="n">
-        <v>-0.103936</v>
+        <v>-0.111</v>
       </c>
       <c r="L402" s="10" t="n">
-        <v>-0.141259</v>
+        <v>-0.133</v>
       </c>
       <c r="M402" s="10" t="n">
-        <v>-0.070535</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="N402" s="10" t="n">
-        <v>-0.04887</v>
+        <v>-0.052</v>
       </c>
       <c r="O402" s="10" t="n">
-        <v>-0.037275</v>
+        <v>-0.036</v>
       </c>
       <c r="P402" s="10" t="n">
-        <v>-0.057376</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="403">
@@ -38395,46 +38395,46 @@
         <v>46054</v>
       </c>
       <c r="C403" s="9" t="n">
-        <v>-0.003493</v>
+        <v>-0.008</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.031041</v>
+        <v>-0.036</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>0.004137</v>
+        <v>0.001</v>
       </c>
       <c r="F403" s="9" t="n">
-        <v>0.016857</v>
+        <v>0.015</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>-0.016352</v>
+        <v>-0.023</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>-0.08269</v>
+        <v>-0.091</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>0.018416</v>
+        <v>0.018</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.014603</v>
+        <v>0.01</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>-0.127045</v>
+        <v>-0.136</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>-0.192642</v>
+        <v>-0.193</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>-0.05941</v>
+        <v>-0.075</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.051622</v>
+        <v>-0.057</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>-0.147523</v>
+        <v>-0.149</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.037447</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="404">
@@ -38447,46 +38447,46 @@
         <v>46082</v>
       </c>
       <c r="C404" s="10" t="n">
-        <v>0.006426</v>
+        <v>0.004</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.026559</v>
+        <v>-0.031</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.020314</v>
+        <v>-0.024</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>-0.025915</v>
+        <v>-0.032</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>0.031961</v>
+        <v>0.031</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>-0.02986</v>
+        <v>-0.032</v>
       </c>
       <c r="I404" s="10" t="n">
-        <v>-0.082258</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>0.034628</v>
+        <v>0.024</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.072811</v>
+        <v>-0.073</v>
       </c>
       <c r="L404" s="10" t="n">
-        <v>-0.128016</v>
+        <v>-0.131</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>-0.01724</v>
+        <v>-0.015</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>-0.012484</v>
+        <v>-0.016</v>
       </c>
       <c r="O404" s="10" t="n">
-        <v>0.068067</v>
+        <v>0.064</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.017561</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="405">
@@ -38499,46 +38499,46 @@
         <v>46113</v>
       </c>
       <c r="C405" s="9" t="n">
-        <v>0.042666</v>
+        <v>0.04</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.053161</v>
+        <v>0.051</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>0.06787899999999999</v>
+        <v>0.065</v>
       </c>
       <c r="F405" s="9" t="n">
-        <v>0.090818</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.020903</v>
+        <v>0.02</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.011111</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>0.16618</v>
+        <v>0.167</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.022099</v>
+        <v>0.011</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>-0.099397</v>
+        <v>-0.106</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>-0.075743</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>-0.120773</v>
+        <v>-0.124</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.08541700000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>-0.009259</v>
+        <v>-0.011</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.097284</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="406">
@@ -38551,46 +38551,46 @@
         <v>46143</v>
       </c>
       <c r="C406" s="10" t="n">
-        <v>-0.004454</v>
+        <v>-0.004</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.023955</v>
+        <v>0.024</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.024821</v>
+        <v>-0.024</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>0.019535</v>
+        <v>0.02</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.014652</v>
+        <v>0.015</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.024369</v>
+        <v>0.025</v>
       </c>
       <c r="I406" s="10" t="n">
-        <v>-0.052105</v>
+        <v>-0.054</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>0.112213</v>
+        <v>0.118</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>-0.073474</v>
+        <v>-0.077</v>
       </c>
       <c r="L406" s="10" t="n">
-        <v>-0.046112</v>
+        <v>-0.05</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>-0.089729</v>
+        <v>-0.091</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.08756799999999999</v>
+        <v>0.089</v>
       </c>
       <c r="O406" s="10" t="n">
-        <v>0.07551099999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>0.092186</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="407">
@@ -38603,46 +38603,46 @@
         <v>46174</v>
       </c>
       <c r="C407" s="9" t="n">
-        <v>0.013515</v>
+        <v>0.013</v>
       </c>
       <c r="D407" s="9" t="n">
-        <v>0.058812</v>
+        <v>0.059</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>0.035409</v>
+        <v>0.035</v>
       </c>
       <c r="F407" s="9" t="n">
-        <v>0.08835999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G407" s="9" t="n">
-        <v>-0.010923</v>
+        <v>-0.011</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>0.02494</v>
+        <v>0.025</v>
       </c>
       <c r="I407" s="9" t="n">
-        <v>0.066577</v>
+        <v>0.067</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>0.106393</v>
+        <v>0.106</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>-0.034195</v>
+        <v>-0.034</v>
       </c>
       <c r="L407" s="9" t="n">
-        <v>-0.007839</v>
+        <v>-0.008</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>-0.060266</v>
+        <v>-0.06</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>0.061515</v>
+        <v>0.062</v>
       </c>
       <c r="O407" s="9" t="n">
-        <v>0.157228</v>
+        <v>0.157</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>0.047343</v>
+        <v>0.047</v>
       </c>
     </row>
   </sheetData>
@@ -38693,7 +38693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -59537,19 +59537,19 @@
         <v>91.53</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.045966</v>
+        <v>-0.029</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>0.03116</v>
+        <v>0.047</v>
       </c>
       <c r="L387" s="7" t="n">
         <v>125.59</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>-0.095564</v>
+        <v>-0.166</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>0.089361</v>
+        <v>0.034</v>
       </c>
       <c r="O387" s="7" t="n">
         <v>121.97</v>
@@ -59592,19 +59592,19 @@
         <v>97.25</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>0.059599</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K388" s="10" t="n">
-        <v>0.033895</v>
+        <v>0.049</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>124.25</v>
       </c>
       <c r="M388" s="10" t="n">
-        <v>-0.111421</v>
+        <v>-0.147</v>
       </c>
       <c r="N388" s="10" t="n">
-        <v>0.067721</v>
+        <v>0.014</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>121.22</v>
@@ -59647,19 +59647,19 @@
         <v>83.88</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>0.001074</v>
+        <v>0.032</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>0.031246</v>
+        <v>0.048</v>
       </c>
       <c r="L389" s="7" t="n">
         <v>134.91</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>-0.135026</v>
+        <v>-0.164</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>0.045963</v>
+        <v>-0.004</v>
       </c>
       <c r="O389" s="7" t="n">
         <v>116.23</v>
@@ -59739,46 +59739,46 @@
         <v>98.64</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.080022</v>
+        <v>-0.078</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>-0.077477</v>
+        <v>-0.074</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.046755</v>
+        <v>-0.052</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.07618</v>
+        <v>-0.079</v>
       </c>
       <c r="I391" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>0.140825</v>
+        <v>0.141</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>0.050031</v>
+        <v>0.056</v>
       </c>
       <c r="L391" s="7" t="n">
         <v>103.42</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.17211</v>
+        <v>-0.18</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.166833</v>
+        <v>-0.174</v>
       </c>
       <c r="O391" s="7" t="n">
         <v>103.31</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.113067</v>
+        <v>-0.104</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>-0.078884</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="392">
@@ -59794,46 +59794,46 @@
         <v>105.87</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.005915</v>
+        <v>-0.002</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>-0.053793</v>
+        <v>-0.049</v>
       </c>
       <c r="F392" s="6" t="n">
         <v>103.35</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>0.001356</v>
+        <v>-0.001</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.050219</v>
+        <v>-0.05</v>
       </c>
       <c r="I392" s="6" t="n">
         <v>105.05</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>0.204564</v>
+        <v>0.205</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>0.103742</v>
+        <v>0.108</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>101.47</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.160156</v>
+        <v>-0.159</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.164661</v>
+        <v>-0.164</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>108.8</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.013689</v>
+        <v>-0.004</v>
       </c>
       <c r="Q392" s="10" t="n">
-        <v>-0.057574</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="393">
@@ -59849,46 +59849,46 @@
         <v>100.25</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.131809</v>
+        <v>-0.125</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.074395</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>98.39</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.100886</v>
+        <v>-0.092</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.06349399999999999</v>
+        <v>-0.061</v>
       </c>
       <c r="I393" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.048008</v>
+        <v>-0.037</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>0.061543</v>
+        <v>0.067</v>
       </c>
       <c r="L393" s="7" t="n">
         <v>105.43</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.146316</v>
+        <v>-0.139</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.160082</v>
+        <v>-0.158</v>
       </c>
       <c r="O393" s="7" t="n">
         <v>102.39</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.16389</v>
+        <v>-0.16</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>-0.085881</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="394">
@@ -59904,46 +59904,46 @@
         <v>107.78</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.06594999999999999</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>-0.072632</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F394" s="6" t="n">
         <v>108.65</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>-0.041634</v>
+        <v>-0.043</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.058827</v>
+        <v>-0.058</v>
       </c>
       <c r="I394" s="6" t="n">
         <v>117.83</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>0.102451</v>
+        <v>0.096</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>0.07116500000000001</v>
+        <v>0.074</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.182241</v>
+        <v>-0.175</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.164421</v>
+        <v>-0.162</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>106.76</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.093179</v>
+        <v>-0.103</v>
       </c>
       <c r="Q394" s="10" t="n">
-        <v>-0.087368</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="395">
@@ -59959,46 +59959,46 @@
         <v>98.92</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.068023</v>
+        <v>-0.064</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.07188899999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.04444</v>
+        <v>-0.032</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.05654</v>
+        <v>-0.054</v>
       </c>
       <c r="I395" s="7" t="n">
         <v>87.73999999999999</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>0.127039</v>
+        <v>0.12</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>0.079336</v>
+        <v>0.082</v>
       </c>
       <c r="L395" s="7" t="n">
         <v>104.88</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.161966</v>
+        <v>-0.137</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.164006</v>
+        <v>-0.159</v>
       </c>
       <c r="O395" s="7" t="n">
         <v>102.41</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.092432</v>
+        <v>-0.097</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>-0.088196</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="396">
@@ -60014,46 +60014,46 @@
         <v>106.74</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.068993</v>
+        <v>-0.066</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.07146</v>
+        <v>-0.068</v>
       </c>
       <c r="F396" s="6" t="n">
         <v>102.77</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>-0.078957</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.059907</v>
+        <v>-0.057</v>
       </c>
       <c r="I396" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>0.058786</v>
+        <v>0.055</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>0.076241</v>
+        <v>0.078</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>105.87</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.188611</v>
+        <v>-0.172</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.167692</v>
+        <v>-0.161</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>111.33</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.058122</v>
+        <v>-0.059</v>
       </c>
       <c r="Q396" s="10" t="n">
-        <v>-0.0838</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="397">
@@ -60069,46 +60069,46 @@
         <v>102.22</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.110434</v>
+        <v>-0.104</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.076501</v>
+        <v>-0.073</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>101.61</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.07391499999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.061709</v>
+        <v>-0.059</v>
       </c>
       <c r="I397" s="7" t="n">
         <v>91.92</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>0.09912700000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>0.07893500000000001</v>
+        <v>0.079</v>
       </c>
       <c r="L397" s="7" t="n">
         <v>112.27</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.189094</v>
+        <v>-0.179</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.170628</v>
+        <v>-0.164</v>
       </c>
       <c r="O397" s="7" t="n">
         <v>102.94</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.148693</v>
+        <v>-0.137</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>-0.092241</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="398">
@@ -60124,46 +60124,46 @@
         <v>99.59</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.067247</v>
+        <v>-0.067</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.07550800000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="F398" s="6" t="n">
         <v>94.42</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>-0.10832</v>
+        <v>-0.106</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.066858</v>
+        <v>-0.067</v>
       </c>
       <c r="I398" s="6" t="n">
         <v>85.19</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.028288</v>
+        <v>-0.031</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>0.06715500000000001</v>
+        <v>0.067</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>104.59</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.169591</v>
+        <v>-0.163</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.170513</v>
+        <v>-0.171</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>105.57</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.020596</v>
+        <v>-0.024</v>
       </c>
       <c r="Q398" s="10" t="n">
-        <v>-0.084797</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="399">
@@ -60179,46 +60179,46 @@
         <v>107.9</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.056241</v>
+        <v>-0.055</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>-0.07352300000000001</v>
+        <v>-0.074</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.008817999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.060994</v>
+        <v>-0.061</v>
       </c>
       <c r="I399" s="7" t="n">
         <v>103.82</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>0.134273</v>
+        <v>0.135</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>0.074062</v>
+        <v>0.074</v>
       </c>
       <c r="L399" s="7" t="n">
         <v>110.07</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.123577</v>
+        <v>-0.122</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.165838</v>
+        <v>-0.167</v>
       </c>
       <c r="O399" s="7" t="n">
         <v>109.17</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.104944</v>
+        <v>-0.105</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>-0.08691599999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -60234,46 +60234,46 @@
         <v>107.74</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.065163</v>
+        <v>-0.064</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>-0.072736</v>
+        <v>-0.073</v>
       </c>
       <c r="F400" s="6" t="n">
         <v>111.27</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>0.010627</v>
+        <v>0.013</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.054291</v>
+        <v>-0.054</v>
       </c>
       <c r="I400" s="6" t="n">
         <v>107.18</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>0.102108</v>
+        <v>0.103</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>0.07682600000000001</v>
+        <v>0.077</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>115.79</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.068089</v>
+        <v>-0.065</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.15707</v>
+        <v>-0.158</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>103.66</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.144861</v>
+        <v>-0.145</v>
       </c>
       <c r="Q400" s="10" t="n">
-        <v>-0.092401</v>
+        <v>-0.093</v>
       </c>
     </row>
     <row r="401">
@@ -60289,46 +60289,46 @@
         <v>111.63</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.002413</v>
+        <v>0</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>-0.06684900000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>112.38</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>0.03892</v>
+        <v>0.043</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.046442</v>
+        <v>-0.046</v>
       </c>
       <c r="I401" s="7" t="n">
         <v>94.72</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>0.129232</v>
+        <v>0.133</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>0.080931</v>
+        <v>0.082</v>
       </c>
       <c r="L401" s="7" t="n">
         <v>131.83</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.02283</v>
+        <v>-0.019</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.145157</v>
+        <v>-0.146</v>
       </c>
       <c r="O401" s="7" t="n">
         <v>110.77</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.046976</v>
+        <v>-0.046</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>-0.08862100000000001</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="402">
@@ -60399,46 +60399,46 @@
         <v>94.67</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.040247</v>
+        <v>-0.042</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>-0.036252</v>
+        <v>-0.037</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>95.65000000000001</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>0.011099</v>
+        <v>0.011</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>0.019111</v>
+        <v>0.02</v>
       </c>
       <c r="I403" s="7" t="n">
         <v>88.31</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.019746</v>
+        <v>0.022</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>0.042644</v>
+        <v>0.045</v>
       </c>
       <c r="L403" s="7" t="n">
         <v>103.73</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>0.002997</v>
+        <v>0.001</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.002395</v>
+        <v>-0.003</v>
       </c>
       <c r="O403" s="7" t="n">
         <v>93.53</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.094667</v>
+        <v>-0.097</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>-0.094289</v>
+        <v>-0.097</v>
       </c>
     </row>
     <row r="404">
@@ -60454,46 +60454,46 @@
         <v>103.31</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.024181</v>
+        <v>-0.026</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.032055</v>
+        <v>-0.033</v>
       </c>
       <c r="F404" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>-0.032414</v>
+        <v>-0.035</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>0.000922</v>
+        <v>0</v>
       </c>
       <c r="I404" s="6" t="n">
         <v>95.81999999999999</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>-0.087863</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.006861</v>
+        <v>-0.007</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>104.6</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>0.030847</v>
+        <v>0.024</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>0.008477999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>107.14</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.015257</v>
+        <v>-0.015</v>
       </c>
       <c r="Q404" s="10" t="n">
-        <v>-0.06725399999999999</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="405">
@@ -60509,46 +60509,46 @@
         <v>106.31</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.060449</v>
+        <v>0.059</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>-0.009142000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F405" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.103364</v>
+        <v>0.101</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.02669</v>
+        <v>0.026</v>
       </c>
       <c r="I405" s="7" t="n">
         <v>108.88</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.18335</v>
+        <v>0.185</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>0.040575</v>
+        <v>0.041</v>
       </c>
       <c r="L405" s="7" t="n">
         <v>108.2</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>0.026273</v>
+        <v>0.02</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.012992</v>
+        <v>0.012</v>
       </c>
       <c r="O405" s="7" t="n">
         <v>103.71</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.012892</v>
+        <v>0.013</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>-0.047736</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="406">
@@ -60564,46 +60564,46 @@
         <v>108.89</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.010299</v>
+        <v>0.011</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.005054</v>
+        <v>-0.005</v>
       </c>
       <c r="F406" s="6" t="n">
         <v>111.32</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.024574</v>
+        <v>0.027</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.02623</v>
+        <v>0.027</v>
       </c>
       <c r="I406" s="6" t="n">
         <v>112.5</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>-0.045235</v>
+        <v>-0.047</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>0.019804</v>
+        <v>0.019</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>110.01</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>0.116399</v>
+        <v>0.124</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.032809</v>
+        <v>0.034</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>106.07</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>-0.006463</v>
+        <v>-0.007</v>
       </c>
       <c r="Q406" s="10" t="n">
-        <v>-0.039378</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="407">
@@ -60619,46 +60619,46 @@
         <v>106.49</v>
       </c>
       <c r="D407" s="9" t="n">
-        <v>0.076526</v>
+        <v>0.077</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>0.008144999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>104.71</v>
       </c>
       <c r="G407" s="9" t="n">
-        <v>0.091867</v>
+        <v>0.092</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>0.036796</v>
+        <v>0.037</v>
       </c>
       <c r="I407" s="7" t="n">
         <v>93.95</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>0.07077700000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>0.027588</v>
+        <v>0.028</v>
       </c>
       <c r="L407" s="7" t="n">
         <v>116.57</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>0.111461</v>
+        <v>0.111</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>0.046134</v>
+        <v>0.046</v>
       </c>
       <c r="O407" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>0.060053</v>
+        <v>0.06</v>
       </c>
       <c r="Q407" s="9" t="n">
-        <v>-0.023205</v>
+        <v>-0.023</v>
       </c>
     </row>
   </sheetData>
@@ -60695,7 +60695,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf · Fecha de publicación: 5 de agosto de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
         </is>
       </c>
     </row>
@@ -60748,7 +60748,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">

--- a/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
+++ b/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
@@ -16978,7 +16978,7 @@
         <v>45566</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>113.1</v>
+        <v>109.27</v>
       </c>
       <c r="D387" s="7" t="n">
         <v>103.61</v>
@@ -17021,7 +17021,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>113.7</v>
+        <v>109.76</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>103.29</v>
@@ -17064,7 +17064,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>109.7</v>
+        <v>106.07</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>101.15</v>
@@ -17107,7 +17107,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>107.4</v>
+        <v>105.19</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>100.33</v>
@@ -17150,7 +17150,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>107.3</v>
+        <v>105.99</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>102.63</v>
@@ -17193,7 +17193,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>107.9</v>
+        <v>106.18</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>104.96</v>
@@ -17236,7 +17236,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>105.6</v>
+        <v>102.33</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>100.09</v>
@@ -17279,7 +17279,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>106.8</v>
+        <v>104.78</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>104.43</v>
@@ -17322,7 +17322,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>105.6</v>
+        <v>102.7</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>101.29</v>
@@ -17365,7 +17365,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>107.5</v>
+        <v>104.79</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>100.96</v>
@@ -17408,7 +17408,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>103.9</v>
+        <v>101.9</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>99.98</v>
@@ -17451,7 +17451,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>101</v>
+        <v>101.99</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>98.02</v>
@@ -17494,7 +17494,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>102.2</v>
+        <v>102.99</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>102.27</v>
@@ -17537,7 +17537,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>102.8</v>
+        <v>103.57</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>103.89</v>
@@ -17580,7 +17580,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>103.6</v>
+        <v>104.02</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>104.89</v>
@@ -17623,7 +17623,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>102.3</v>
+        <v>103.06</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>103.93</v>
@@ -17666,7 +17666,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>101.1</v>
+        <v>102.7</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>104.36</v>
@@ -17709,7 +17709,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>102</v>
+        <v>103.36</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>102.24</v>
@@ -17752,7 +17752,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>107.4</v>
+        <v>107.77</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>109.18</v>
@@ -17795,7 +17795,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>107.1</v>
+        <v>107.29</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>106.47</v>
@@ -17838,7 +17838,7 @@
         <v>46174</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>108.7</v>
+        <v>108.74</v>
       </c>
       <c r="D407" s="7" t="n">
         <v>110.24</v>
@@ -37563,10 +37563,10 @@
         <v>45566</v>
       </c>
       <c r="C387" s="9" t="n">
-        <v>0.001</v>
+        <v>-0.015231</v>
       </c>
       <c r="D387" s="9" t="n">
-        <v>-0.045</v>
+        <v>-0.033864</v>
       </c>
       <c r="E387" s="9" t="n">
         <v>-0.046387</v>
@@ -37581,10 +37581,10 @@
         <v>0.023488</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>-0.035</v>
+        <v>-0.060137</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.092969</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>0.000555</v>
@@ -37615,10 +37615,10 @@
         <v>45597</v>
       </c>
       <c r="C388" s="10" t="n">
-        <v>0.001</v>
+        <v>0.004484</v>
       </c>
       <c r="D388" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.003993</v>
       </c>
       <c r="E388" s="10" t="n">
         <v>-0.003089</v>
@@ -37633,10 +37633,10 @@
         <v>0.047964</v>
       </c>
       <c r="I388" s="10" t="n">
-        <v>0.068</v>
+        <v>0.046145</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>-0.148</v>
+        <v>-0.11381</v>
       </c>
       <c r="K388" s="10" t="n">
         <v>0.057398</v>
@@ -37667,10 +37667,10 @@
         <v>45627</v>
       </c>
       <c r="C389" s="9" t="n">
-        <v>-0.026</v>
+        <v>-0.033619</v>
       </c>
       <c r="D389" s="9" t="n">
-        <v>-0.041</v>
+        <v>-0.050233</v>
       </c>
       <c r="E389" s="9" t="n">
         <v>-0.020718</v>
@@ -37685,10 +37685,10 @@
         <v>-0.006644</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>0.043</v>
+        <v>0.013939</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>-0.171</v>
+        <v>-0.150682</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>-0.018671</v>
@@ -37719,46 +37719,46 @@
         <v>45658</v>
       </c>
       <c r="C390" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.008296</v>
       </c>
       <c r="D390" s="10" t="n">
-        <v>-0.059</v>
+        <v>-0.06506099999999999</v>
       </c>
       <c r="E390" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.008107</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>-0.09</v>
+        <v>-0.088738</v>
       </c>
       <c r="G390" s="10" t="n">
-        <v>-0.018</v>
+        <v>-0.01079</v>
       </c>
       <c r="H390" s="10" t="n">
-        <v>-0.023</v>
+        <v>-0.03514</v>
       </c>
       <c r="I390" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.017972</v>
       </c>
       <c r="J390" s="10" t="n">
-        <v>-0.142</v>
+        <v>-0.151065</v>
       </c>
       <c r="K390" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.06428499999999999</v>
       </c>
       <c r="L390" s="10" t="n">
-        <v>0.022</v>
+        <v>-0.021327</v>
       </c>
       <c r="M390" s="10" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.113759</v>
       </c>
       <c r="N390" s="10" t="n">
-        <v>-0.016</v>
+        <v>-0.017595</v>
       </c>
       <c r="O390" s="10" t="n">
-        <v>-0.136</v>
+        <v>-0.132904</v>
       </c>
       <c r="P390" s="10" t="n">
-        <v>-0.001</v>
+        <v>-0.003057</v>
       </c>
     </row>
     <row r="391">
@@ -37771,46 +37771,46 @@
         <v>45689</v>
       </c>
       <c r="C391" s="9" t="n">
-        <v>0.001</v>
+        <v>0.007605</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.06</v>
+        <v>-0.057028</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>0.017</v>
+        <v>0.022924</v>
       </c>
       <c r="F391" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.040393</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.006851</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.063</v>
+        <v>-0.06683</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>0.128</v>
+        <v>0.136052</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>-0.168</v>
+        <v>-0.158461</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>-0.021</v>
+        <v>-0.048012</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>0.021</v>
+        <v>-0.013586</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.077</v>
+        <v>-0.083468</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.093</v>
+        <v>-0.081163</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>-0.081</v>
+        <v>-0.076588</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.08068699999999999</v>
       </c>
     </row>
     <row r="392">
@@ -37823,46 +37823,46 @@
         <v>45717</v>
       </c>
       <c r="C392" s="10" t="n">
-        <v>0.003</v>
+        <v>0.001793</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.047</v>
+        <v>-0.049843</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>0.008</v>
+        <v>0.022703</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.022719</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.024235</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.075</v>
+        <v>-0.08502899999999999</v>
       </c>
       <c r="I392" s="10" t="n">
-        <v>0.147</v>
+        <v>0.166975</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>-0.171</v>
+        <v>-0.168503</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>-0.066</v>
+        <v>-0.089406</v>
       </c>
       <c r="L392" s="10" t="n">
-        <v>-0.1</v>
+        <v>-0.122053</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.045061</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.08</v>
+        <v>-0.083105</v>
       </c>
       <c r="O392" s="10" t="n">
-        <v>-0.148</v>
+        <v>-0.144005</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.077</v>
+        <v>-0.080719</v>
       </c>
     </row>
     <row r="393">
@@ -37875,46 +37875,46 @@
         <v>45748</v>
       </c>
       <c r="C393" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.036259</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.077</v>
+        <v>-0.088212</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.046399</v>
       </c>
       <c r="F393" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.071866</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.022</v>
+        <v>-0.020465</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.091</v>
+        <v>-0.096525</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>0.024</v>
+        <v>-0.004026</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.118</v>
+        <v>-0.1306</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>-0.083</v>
+        <v>-0.08184900000000001</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>-0.143</v>
+        <v>-0.150113</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.012903</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.091</v>
+        <v>-0.098775</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>-0.073</v>
+        <v>-0.081743</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.091323</v>
       </c>
     </row>
     <row r="394">
@@ -37927,46 +37927,46 @@
         <v>45778</v>
       </c>
       <c r="C394" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023942</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.067</v>
+        <v>-0.063628</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>0.014</v>
+        <v>0.043361</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.048994</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>0</v>
+        <v>0.001519</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.082</v>
+        <v>-0.077663</v>
       </c>
       <c r="I394" s="10" t="n">
-        <v>0.079</v>
+        <v>0.087355</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>-0.171</v>
+        <v>-0.184172</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>-0.034</v>
+        <v>-0.025784</v>
       </c>
       <c r="L394" s="10" t="n">
-        <v>-0.055</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.019</v>
+        <v>0.027141</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.106</v>
+        <v>-0.105678</v>
       </c>
       <c r="O394" s="10" t="n">
-        <v>-0.267</v>
+        <v>-0.255997</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07587099999999999</v>
       </c>
     </row>
     <row r="395">
@@ -37979,46 +37979,46 @@
         <v>45809</v>
       </c>
       <c r="C395" s="9" t="n">
-        <v>-0.014</v>
+        <v>-0.019851</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.068</v>
+        <v>-0.073439</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.030068</v>
       </c>
       <c r="F395" s="9" t="n">
-        <v>-0.033</v>
+        <v>-0.050614</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.011474</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.114</v>
+        <v>-0.108593</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>0.118</v>
+        <v>0.120577</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>-0.138</v>
+        <v>-0.169159</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>-0.132</v>
+        <v>-0.125315</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>-0.155</v>
+        <v>-0.165292</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.114</v>
+        <v>-0.088338</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.096</v>
+        <v>-0.09321500000000001</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>-0.148</v>
+        <v>-0.151315</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.081</v>
+        <v>-0.078399</v>
       </c>
     </row>
     <row r="396">
@@ -38031,46 +38031,46 @@
         <v>45839</v>
       </c>
       <c r="C396" s="10" t="n">
-        <v>0.016</v>
+        <v>0.020351</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07649599999999999</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.013</v>
+        <v>-0.003258</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>-0.075</v>
+        <v>-0.086252</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>0.049</v>
+        <v>0.040096</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.059</v>
+        <v>-0.060399</v>
       </c>
       <c r="I396" s="10" t="n">
-        <v>0.046</v>
+        <v>0.048097</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>-0.176</v>
+        <v>-0.193215</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>-0.114</v>
+        <v>-0.113547</v>
       </c>
       <c r="L396" s="10" t="n">
-        <v>-0.172</v>
+        <v>-0.180201</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.049</v>
+        <v>-0.045172</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.030134</v>
       </c>
       <c r="O396" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.050938</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.023</v>
+        <v>-0.028977</v>
       </c>
     </row>
     <row r="397">
@@ -38083,46 +38083,46 @@
         <v>45870</v>
       </c>
       <c r="C397" s="9" t="n">
-        <v>-0.027</v>
+        <v>-0.027579</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.089</v>
+        <v>-0.09365800000000001</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.015</v>
+        <v>-0.009707</v>
       </c>
       <c r="F397" s="9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.07012599999999999</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.031</v>
+        <v>-0.038642</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.105</v>
+        <v>-0.116685</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>0.1</v>
+        <v>0.113731</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>-0.185</v>
+        <v>-0.193116</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.125123</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>-0.123</v>
+        <v>-0.136581</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.056</v>
+        <v>-0.120682</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.119</v>
+        <v>-0.116669</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>-0.154</v>
+        <v>-0.152947</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.11</v>
+        <v>-0.105424</v>
       </c>
     </row>
     <row r="398">
@@ -38135,46 +38135,46 @@
         <v>45901</v>
       </c>
       <c r="C398" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.000883</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.08084</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.026</v>
+        <v>-0.019604</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>-0.102</v>
+        <v>-0.09783699999999999</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>0.019</v>
+        <v>0.017076</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.061</v>
+        <v>-0.064914</v>
       </c>
       <c r="I398" s="10" t="n">
-        <v>-0.02</v>
+        <v>-0.014319</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.164</v>
+        <v>-0.163128</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>-0.106</v>
+        <v>-0.111293</v>
       </c>
       <c r="L398" s="10" t="n">
-        <v>-0.168</v>
+        <v>-0.173014</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.045612</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.033</v>
+        <v>-0.032397</v>
       </c>
       <c r="O398" s="10" t="n">
-        <v>-0.164</v>
+        <v>-0.159101</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.006</v>
+        <v>-0.005226</v>
       </c>
     </row>
     <row r="399">
@@ -38187,46 +38187,46 @@
         <v>45931</v>
       </c>
       <c r="C399" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009804999999999999</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.058</v>
+        <v>-0.057472</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>0.039</v>
+        <v>0.043358</v>
       </c>
       <c r="F399" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.012933</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.022</v>
+        <v>-0.023109</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.103</v>
+        <v>-0.106462</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>0.118</v>
+        <v>0.123878</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>-0.126</v>
+        <v>-0.120615</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>-0.118</v>
+        <v>-0.120803</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>-0.171</v>
+        <v>-0.172389</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.047</v>
+        <v>-0.052672</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.094</v>
+        <v>-0.095438</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>-0.132</v>
+        <v>-0.128135</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.089714</v>
       </c>
     </row>
     <row r="400">
@@ -38239,46 +38239,46 @@
         <v>45962</v>
       </c>
       <c r="C400" s="10" t="n">
-        <v>0.004</v>
+        <v>0.005632</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.057</v>
+        <v>-0.056396</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>0.015</v>
+        <v>0.01584</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>0.006</v>
+        <v>0.005809</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.000386</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.116</v>
+        <v>-0.117617</v>
       </c>
       <c r="I400" s="10" t="n">
-        <v>0.092</v>
+        <v>0.09261900000000001</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06814099999999999</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>-0.152</v>
+        <v>-0.153321</v>
       </c>
       <c r="L400" s="10" t="n">
-        <v>-0.187</v>
+        <v>-0.191233</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.101</v>
+        <v>-0.103515</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.091</v>
+        <v>-0.09116299999999999</v>
       </c>
       <c r="O400" s="10" t="n">
-        <v>-0.191</v>
+        <v>-0.187012</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.075</v>
+        <v>-0.078113</v>
       </c>
     </row>
     <row r="401">
@@ -38291,46 +38291,46 @@
         <v>45992</v>
       </c>
       <c r="C401" s="9" t="n">
-        <v>0.005</v>
+        <v>0.004345</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.019327</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009625999999999999</v>
       </c>
       <c r="F401" s="9" t="n">
-        <v>0.041</v>
+        <v>0.036975</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>-0.003</v>
+        <v>-0.001449</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.079</v>
+        <v>-0.07811700000000001</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>0.142</v>
+        <v>0.140108</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>-0.03</v>
+        <v>-0.032893</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>-0.118</v>
+        <v>-0.118436</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>-0.163</v>
+        <v>-0.166199</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.053</v>
+        <v>-0.05462</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.049</v>
+        <v>-0.048424</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>-0.027</v>
+        <v>-0.033469</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.05</v>
+        <v>-0.048545</v>
       </c>
     </row>
     <row r="402">
@@ -38343,46 +38343,46 @@
         <v>46023</v>
       </c>
       <c r="C402" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.009228999999999999</v>
       </c>
       <c r="D402" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.020249</v>
       </c>
       <c r="E402" s="10" t="n">
-        <v>-0.008</v>
+        <v>-0.009152</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>0.038</v>
+        <v>0.035882</v>
       </c>
       <c r="G402" s="10" t="n">
-        <v>-0.011</v>
+        <v>-0.006191</v>
       </c>
       <c r="H402" s="10" t="n">
-        <v>-0.08</v>
+        <v>-0.07383000000000001</v>
       </c>
       <c r="I402" s="10" t="n">
-        <v>0.079</v>
+        <v>0.078083</v>
       </c>
       <c r="J402" s="10" t="n">
-        <v>0</v>
+        <v>-0.001165</v>
       </c>
       <c r="K402" s="10" t="n">
-        <v>-0.111</v>
+        <v>-0.103936</v>
       </c>
       <c r="L402" s="10" t="n">
-        <v>-0.133</v>
+        <v>-0.141259</v>
       </c>
       <c r="M402" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.070535</v>
       </c>
       <c r="N402" s="10" t="n">
-        <v>-0.052</v>
+        <v>-0.04887</v>
       </c>
       <c r="O402" s="10" t="n">
-        <v>-0.036</v>
+        <v>-0.037275</v>
       </c>
       <c r="P402" s="10" t="n">
-        <v>-0.063</v>
+        <v>-0.057376</v>
       </c>
     </row>
     <row r="403">
@@ -38395,46 +38395,46 @@
         <v>46054</v>
       </c>
       <c r="C403" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.003493</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.036</v>
+        <v>-0.031041</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>0.001</v>
+        <v>0.004137</v>
       </c>
       <c r="F403" s="9" t="n">
-        <v>0.015</v>
+        <v>0.016857</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>-0.023</v>
+        <v>-0.016352</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>-0.091</v>
+        <v>-0.08269</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>0.018</v>
+        <v>0.018416</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.01</v>
+        <v>0.014603</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>-0.136</v>
+        <v>-0.127045</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>-0.193</v>
+        <v>-0.192642</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>-0.075</v>
+        <v>-0.05941</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.057</v>
+        <v>-0.051622</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>-0.149</v>
+        <v>-0.147523</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.047</v>
+        <v>-0.037447</v>
       </c>
     </row>
     <row r="404">
@@ -38447,46 +38447,46 @@
         <v>46082</v>
       </c>
       <c r="C404" s="10" t="n">
-        <v>0.004</v>
+        <v>0.006426</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.026559</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.020314</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.025915</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>0.031</v>
+        <v>0.031961</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.02986</v>
       </c>
       <c r="I404" s="10" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.082258</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>0.024</v>
+        <v>0.034628</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.073</v>
+        <v>-0.072811</v>
       </c>
       <c r="L404" s="10" t="n">
-        <v>-0.131</v>
+        <v>-0.128016</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.01724</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>-0.016</v>
+        <v>-0.012484</v>
       </c>
       <c r="O404" s="10" t="n">
-        <v>0.064</v>
+        <v>0.068067</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.017561</v>
       </c>
     </row>
     <row r="405">
@@ -38499,46 +38499,46 @@
         <v>46113</v>
       </c>
       <c r="C405" s="9" t="n">
-        <v>0.04</v>
+        <v>0.042666</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.051</v>
+        <v>0.053161</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>0.065</v>
+        <v>0.06787899999999999</v>
       </c>
       <c r="F405" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.090818</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.02</v>
+        <v>0.020903</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011111</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>0.167</v>
+        <v>0.16618</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.011</v>
+        <v>0.022099</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>-0.106</v>
+        <v>-0.099397</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.075743</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>-0.124</v>
+        <v>-0.120773</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08541700000000001</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.009259</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.098</v>
+        <v>0.097284</v>
       </c>
     </row>
     <row r="406">
@@ -38551,46 +38551,46 @@
         <v>46143</v>
       </c>
       <c r="C406" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.004454</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.024</v>
+        <v>0.023955</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.024821</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>0.02</v>
+        <v>0.019535</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.015</v>
+        <v>0.014652</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.025</v>
+        <v>0.024369</v>
       </c>
       <c r="I406" s="10" t="n">
-        <v>-0.054</v>
+        <v>-0.052105</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>0.118</v>
+        <v>0.112213</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>-0.077</v>
+        <v>-0.073474</v>
       </c>
       <c r="L406" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.046112</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>-0.091</v>
+        <v>-0.089729</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.089</v>
+        <v>0.08756799999999999</v>
       </c>
       <c r="O406" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07551099999999999</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>0.097</v>
+        <v>0.092186</v>
       </c>
     </row>
     <row r="407">
@@ -38603,46 +38603,46 @@
         <v>46174</v>
       </c>
       <c r="C407" s="9" t="n">
-        <v>0.013</v>
+        <v>0.013515</v>
       </c>
       <c r="D407" s="9" t="n">
-        <v>0.059</v>
+        <v>0.058812</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>0.035</v>
+        <v>0.035409</v>
       </c>
       <c r="F407" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08835999999999999</v>
       </c>
       <c r="G407" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.010923</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>0.025</v>
+        <v>0.02494</v>
       </c>
       <c r="I407" s="9" t="n">
-        <v>0.067</v>
+        <v>0.066577</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>0.106</v>
+        <v>0.106393</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>-0.034</v>
+        <v>-0.034195</v>
       </c>
       <c r="L407" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.007839</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>-0.06</v>
+        <v>-0.060266</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>0.062</v>
+        <v>0.061515</v>
       </c>
       <c r="O407" s="9" t="n">
-        <v>0.157</v>
+        <v>0.157228</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>0.047</v>
+        <v>0.047343</v>
       </c>
     </row>
   </sheetData>
@@ -59537,19 +59537,19 @@
         <v>91.53</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.029</v>
+        <v>-0.045966</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>0.047</v>
+        <v>0.03116</v>
       </c>
       <c r="L387" s="7" t="n">
         <v>125.59</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>-0.166</v>
+        <v>-0.095564</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>0.034</v>
+        <v>0.089361</v>
       </c>
       <c r="O387" s="7" t="n">
         <v>121.97</v>
@@ -59592,19 +59592,19 @@
         <v>97.25</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.059599</v>
       </c>
       <c r="K388" s="10" t="n">
-        <v>0.049</v>
+        <v>0.033895</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>124.25</v>
       </c>
       <c r="M388" s="10" t="n">
-        <v>-0.147</v>
+        <v>-0.111421</v>
       </c>
       <c r="N388" s="10" t="n">
-        <v>0.014</v>
+        <v>0.067721</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>121.22</v>
@@ -59647,19 +59647,19 @@
         <v>83.88</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>0.032</v>
+        <v>0.001074</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>0.048</v>
+        <v>0.031246</v>
       </c>
       <c r="L389" s="7" t="n">
         <v>134.91</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>-0.164</v>
+        <v>-0.135026</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>-0.004</v>
+        <v>0.045963</v>
       </c>
       <c r="O389" s="7" t="n">
         <v>116.23</v>
@@ -59739,46 +59739,46 @@
         <v>98.64</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.078</v>
+        <v>-0.080022</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>-0.074</v>
+        <v>-0.077477</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.052</v>
+        <v>-0.046755</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.079</v>
+        <v>-0.07618</v>
       </c>
       <c r="I391" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>0.141</v>
+        <v>0.140825</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>0.056</v>
+        <v>0.050031</v>
       </c>
       <c r="L391" s="7" t="n">
         <v>103.42</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.18</v>
+        <v>-0.17211</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.174</v>
+        <v>-0.166833</v>
       </c>
       <c r="O391" s="7" t="n">
         <v>103.31</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.104</v>
+        <v>-0.113067</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.078884</v>
       </c>
     </row>
     <row r="392">
@@ -59794,46 +59794,46 @@
         <v>105.87</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.005915</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>-0.049</v>
+        <v>-0.053793</v>
       </c>
       <c r="F392" s="6" t="n">
         <v>103.35</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.001</v>
+        <v>0.001356</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.050219</v>
       </c>
       <c r="I392" s="6" t="n">
         <v>105.05</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>0.205</v>
+        <v>0.204564</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>0.108</v>
+        <v>0.103742</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>101.47</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.159</v>
+        <v>-0.160156</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.164</v>
+        <v>-0.164661</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>108.8</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.013689</v>
       </c>
       <c r="Q392" s="10" t="n">
-        <v>-0.047</v>
+        <v>-0.057574</v>
       </c>
     </row>
     <row r="393">
@@ -59849,46 +59849,46 @@
         <v>100.25</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.125</v>
+        <v>-0.131809</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.074395</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>98.39</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.092</v>
+        <v>-0.100886</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.061</v>
+        <v>-0.06349399999999999</v>
       </c>
       <c r="I393" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.037</v>
+        <v>-0.048008</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>0.067</v>
+        <v>0.061543</v>
       </c>
       <c r="L393" s="7" t="n">
         <v>105.43</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.139</v>
+        <v>-0.146316</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.158</v>
+        <v>-0.160082</v>
       </c>
       <c r="O393" s="7" t="n">
         <v>102.39</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.16</v>
+        <v>-0.16389</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>-0.077</v>
+        <v>-0.085881</v>
       </c>
     </row>
     <row r="394">
@@ -59904,46 +59904,46 @@
         <v>107.78</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.06594999999999999</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.072632</v>
       </c>
       <c r="F394" s="6" t="n">
         <v>108.65</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>-0.043</v>
+        <v>-0.041634</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.058</v>
+        <v>-0.058827</v>
       </c>
       <c r="I394" s="6" t="n">
         <v>117.83</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>0.096</v>
+        <v>0.102451</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>0.074</v>
+        <v>0.07116500000000001</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.175</v>
+        <v>-0.182241</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.162</v>
+        <v>-0.164421</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>106.76</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.103</v>
+        <v>-0.093179</v>
       </c>
       <c r="Q394" s="10" t="n">
-        <v>-0.082</v>
+        <v>-0.087368</v>
       </c>
     </row>
     <row r="395">
@@ -59959,46 +59959,46 @@
         <v>98.92</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.064</v>
+        <v>-0.068023</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.07188899999999999</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.032</v>
+        <v>-0.04444</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.054</v>
+        <v>-0.05654</v>
       </c>
       <c r="I395" s="7" t="n">
         <v>87.73999999999999</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>0.12</v>
+        <v>0.127039</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>0.082</v>
+        <v>0.079336</v>
       </c>
       <c r="L395" s="7" t="n">
         <v>104.88</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.137</v>
+        <v>-0.161966</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.159</v>
+        <v>-0.164006</v>
       </c>
       <c r="O395" s="7" t="n">
         <v>102.41</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.097</v>
+        <v>-0.092432</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.088196</v>
       </c>
     </row>
     <row r="396">
@@ -60014,46 +60014,46 @@
         <v>106.74</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.066</v>
+        <v>-0.068993</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.068</v>
+        <v>-0.07146</v>
       </c>
       <c r="F396" s="6" t="n">
         <v>102.77</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.078957</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.057</v>
+        <v>-0.059907</v>
       </c>
       <c r="I396" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>0.055</v>
+        <v>0.058786</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>0.078</v>
+        <v>0.076241</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>105.87</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.172</v>
+        <v>-0.188611</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.161</v>
+        <v>-0.167692</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>111.33</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.059</v>
+        <v>-0.058122</v>
       </c>
       <c r="Q396" s="10" t="n">
-        <v>-0.081</v>
+        <v>-0.0838</v>
       </c>
     </row>
     <row r="397">
@@ -60069,46 +60069,46 @@
         <v>102.22</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.104</v>
+        <v>-0.110434</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.073</v>
+        <v>-0.076501</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>101.61</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.074</v>
+        <v>-0.07391499999999999</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.061709</v>
       </c>
       <c r="I397" s="7" t="n">
         <v>91.92</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09912700000000001</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>0.079</v>
+        <v>0.07893500000000001</v>
       </c>
       <c r="L397" s="7" t="n">
         <v>112.27</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.179</v>
+        <v>-0.189094</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.164</v>
+        <v>-0.170628</v>
       </c>
       <c r="O397" s="7" t="n">
         <v>102.94</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.137</v>
+        <v>-0.148693</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.092241</v>
       </c>
     </row>
     <row r="398">
@@ -60124,46 +60124,46 @@
         <v>99.59</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.067</v>
+        <v>-0.067247</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.076</v>
+        <v>-0.07550800000000001</v>
       </c>
       <c r="F398" s="6" t="n">
         <v>94.42</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>-0.106</v>
+        <v>-0.10832</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.067</v>
+        <v>-0.066858</v>
       </c>
       <c r="I398" s="6" t="n">
         <v>85.19</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.031</v>
+        <v>-0.028288</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>0.067</v>
+        <v>0.06715500000000001</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>104.59</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.163</v>
+        <v>-0.169591</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.171</v>
+        <v>-0.170513</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>105.57</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.020596</v>
       </c>
       <c r="Q398" s="10" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.084797</v>
       </c>
     </row>
     <row r="399">
@@ -60179,46 +60179,46 @@
         <v>107.9</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.055</v>
+        <v>-0.056241</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>-0.074</v>
+        <v>-0.07352300000000001</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.007</v>
+        <v>-0.008817999999999999</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.061</v>
+        <v>-0.060994</v>
       </c>
       <c r="I399" s="7" t="n">
         <v>103.82</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>0.135</v>
+        <v>0.134273</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>0.074</v>
+        <v>0.074062</v>
       </c>
       <c r="L399" s="7" t="n">
         <v>110.07</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.122</v>
+        <v>-0.123577</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.167</v>
+        <v>-0.165838</v>
       </c>
       <c r="O399" s="7" t="n">
         <v>109.17</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.105</v>
+        <v>-0.104944</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.08691599999999999</v>
       </c>
     </row>
     <row r="400">
@@ -60234,46 +60234,46 @@
         <v>107.74</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.064</v>
+        <v>-0.065163</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>-0.073</v>
+        <v>-0.072736</v>
       </c>
       <c r="F400" s="6" t="n">
         <v>111.27</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>0.013</v>
+        <v>0.010627</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.054</v>
+        <v>-0.054291</v>
       </c>
       <c r="I400" s="6" t="n">
         <v>107.18</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>0.103</v>
+        <v>0.102108</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>0.077</v>
+        <v>0.07682600000000001</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>115.79</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.065</v>
+        <v>-0.068089</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.158</v>
+        <v>-0.15707</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>103.66</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.145</v>
+        <v>-0.144861</v>
       </c>
       <c r="Q400" s="10" t="n">
-        <v>-0.093</v>
+        <v>-0.092401</v>
       </c>
     </row>
     <row r="401">
@@ -60289,46 +60289,46 @@
         <v>111.63</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>0</v>
+        <v>-0.002413</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>-0.067</v>
+        <v>-0.06684900000000001</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>112.38</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>0.043</v>
+        <v>0.03892</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.046</v>
+        <v>-0.046442</v>
       </c>
       <c r="I401" s="7" t="n">
         <v>94.72</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>0.133</v>
+        <v>0.129232</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>0.082</v>
+        <v>0.080931</v>
       </c>
       <c r="L401" s="7" t="n">
         <v>131.83</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.02283</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.146</v>
+        <v>-0.145157</v>
       </c>
       <c r="O401" s="7" t="n">
         <v>110.77</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.046</v>
+        <v>-0.046976</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>-0.09</v>
+        <v>-0.08862100000000001</v>
       </c>
     </row>
     <row r="402">
@@ -60399,46 +60399,46 @@
         <v>94.67</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.042</v>
+        <v>-0.040247</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>-0.037</v>
+        <v>-0.036252</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>95.65000000000001</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>0.011</v>
+        <v>0.011099</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>0.02</v>
+        <v>0.019111</v>
       </c>
       <c r="I403" s="7" t="n">
         <v>88.31</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.022</v>
+        <v>0.019746</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>0.045</v>
+        <v>0.042644</v>
       </c>
       <c r="L403" s="7" t="n">
         <v>103.73</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>0.001</v>
+        <v>0.002997</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.003</v>
+        <v>-0.002395</v>
       </c>
       <c r="O403" s="7" t="n">
         <v>93.53</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.097</v>
+        <v>-0.094667</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>-0.097</v>
+        <v>-0.094289</v>
       </c>
     </row>
     <row r="404">
@@ -60454,46 +60454,46 @@
         <v>103.31</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.026</v>
+        <v>-0.024181</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.033</v>
+        <v>-0.032055</v>
       </c>
       <c r="F404" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>-0.035</v>
+        <v>-0.032414</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>0</v>
+        <v>0.000922</v>
       </c>
       <c r="I404" s="6" t="n">
         <v>95.81999999999999</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.087863</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.006861</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>104.6</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>0.024</v>
+        <v>0.030847</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>0.006</v>
+        <v>0.008477999999999999</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>107.14</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.015</v>
+        <v>-0.015257</v>
       </c>
       <c r="Q404" s="10" t="n">
-        <v>-0.068</v>
+        <v>-0.06725399999999999</v>
       </c>
     </row>
     <row r="405">
@@ -60509,46 +60509,46 @@
         <v>106.31</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.059</v>
+        <v>0.060449</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.009142000000000001</v>
       </c>
       <c r="F405" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.101</v>
+        <v>0.103364</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.026</v>
+        <v>0.02669</v>
       </c>
       <c r="I405" s="7" t="n">
         <v>108.88</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.185</v>
+        <v>0.18335</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>0.041</v>
+        <v>0.040575</v>
       </c>
       <c r="L405" s="7" t="n">
         <v>108.2</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>0.02</v>
+        <v>0.026273</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.012</v>
+        <v>0.012992</v>
       </c>
       <c r="O405" s="7" t="n">
         <v>103.71</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.013</v>
+        <v>0.012892</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>-0.048</v>
+        <v>-0.047736</v>
       </c>
     </row>
     <row r="406">
@@ -60564,46 +60564,46 @@
         <v>108.89</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.011</v>
+        <v>0.010299</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.005</v>
+        <v>-0.005054</v>
       </c>
       <c r="F406" s="6" t="n">
         <v>111.32</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.027</v>
+        <v>0.024574</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.027</v>
+        <v>0.02623</v>
       </c>
       <c r="I406" s="6" t="n">
         <v>112.5</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>-0.047</v>
+        <v>-0.045235</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>0.019</v>
+        <v>0.019804</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>110.01</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>0.124</v>
+        <v>0.116399</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.034</v>
+        <v>0.032809</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>106.07</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.006463</v>
       </c>
       <c r="Q406" s="10" t="n">
-        <v>-0.04</v>
+        <v>-0.039378</v>
       </c>
     </row>
     <row r="407">
@@ -60619,46 +60619,46 @@
         <v>106.49</v>
       </c>
       <c r="D407" s="9" t="n">
-        <v>0.077</v>
+        <v>0.076526</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>0.008</v>
+        <v>0.008144999999999999</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>104.71</v>
       </c>
       <c r="G407" s="9" t="n">
-        <v>0.092</v>
+        <v>0.091867</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>0.037</v>
+        <v>0.036796</v>
       </c>
       <c r="I407" s="7" t="n">
         <v>93.95</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07077700000000001</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>0.028</v>
+        <v>0.027588</v>
       </c>
       <c r="L407" s="7" t="n">
         <v>116.57</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>0.111</v>
+        <v>0.111461</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>0.046</v>
+        <v>0.046134</v>
       </c>
       <c r="O407" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>0.06</v>
+        <v>0.060053</v>
       </c>
       <c r="Q407" s="9" t="n">
-        <v>-0.023</v>
+        <v>-0.023205</v>
       </c>
     </row>
   </sheetData>
@@ -60748,7 +60748,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>+1.3%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
